--- a/data/btoa_traffic_analysis.xlsx
+++ b/data/btoa_traffic_analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -13287,7 +13287,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:58 UTC</t>
+          <t>Rebuilt: 2026-09-11 19:59 UTC</t>
         </is>
       </c>
     </row>

--- a/data/btoa_traffic_analysis.xlsx
+++ b/data/btoa_traffic_analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,14 +436,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:F274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,6 +470,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
@@ -488,7 +494,7 @@
       <c r="D2" t="n">
         <v>308890</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -509,7 +515,10 @@
       <c r="D3" t="n">
         <v>305531</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -530,7 +539,10 @@
       <c r="D4" t="n">
         <v>818</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -551,7 +563,7 @@
       <c r="D5" t="n">
         <v>305193</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -572,7 +584,10 @@
       <c r="D6" t="n">
         <v>301919</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -593,7 +608,10 @@
       <c r="D7" t="n">
         <v>834</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -614,7 +632,7 @@
       <c r="D8" t="n">
         <v>356068</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -635,7 +653,10 @@
       <c r="D9" t="n">
         <v>352582</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -656,7 +677,10 @@
       <c r="D10" t="n">
         <v>895</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -677,7 +701,7 @@
       <c r="D11" t="n">
         <v>351274</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -698,7 +722,10 @@
       <c r="D12" t="n">
         <v>347738</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -719,7 +746,10 @@
       <c r="D13" t="n">
         <v>980</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -740,7 +770,7 @@
       <c r="D14" t="n">
         <v>366710</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -761,7 +791,10 @@
       <c r="D15" t="n">
         <v>363015</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -782,7 +815,10 @@
       <c r="D16" t="n">
         <v>1057</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -803,7 +839,7 @@
       <c r="D17" t="n">
         <v>356824</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -824,7 +860,10 @@
       <c r="D18" t="n">
         <v>353264</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -845,7 +884,10 @@
       <c r="D19" t="n">
         <v>969</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -866,7 +908,7 @@
       <c r="D20" t="n">
         <v>355661</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -887,7 +929,10 @@
       <c r="D21" t="n">
         <v>352049</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -908,7 +953,10 @@
       <c r="D22" t="n">
         <v>964</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -929,7 +977,7 @@
       <c r="D23" t="n">
         <v>390049</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -950,7 +998,10 @@
       <c r="D24" t="n">
         <v>386184</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -971,7 +1022,10 @@
       <c r="D25" t="n">
         <v>1009</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -992,7 +1046,7 @@
       <c r="D26" t="n">
         <v>358837</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1013,7 +1067,10 @@
       <c r="D27" t="n">
         <v>355165</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1034,7 +1091,10 @@
       <c r="D28" t="n">
         <v>928</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1055,7 +1115,7 @@
       <c r="D29" t="n">
         <v>367152</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1076,7 +1136,10 @@
       <c r="D30" t="n">
         <v>363343</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1097,7 +1160,10 @@
       <c r="D31" t="n">
         <v>1019</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1118,7 +1184,7 @@
       <c r="D32" t="n">
         <v>344698</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1139,7 +1205,10 @@
       <c r="D33" t="n">
         <v>341197</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1160,7 +1229,10 @@
       <c r="D34" t="n">
         <v>916</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1181,7 +1253,7 @@
       <c r="D35" t="n">
         <v>358561</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1202,7 +1274,10 @@
       <c r="D36" t="n">
         <v>355306</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1223,7 +1298,10 @@
       <c r="D37" t="n">
         <v>757</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1244,7 +1322,7 @@
       <c r="D38" t="n">
         <v>334640</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1265,7 +1343,10 @@
       <c r="D39" t="n">
         <v>331282</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1286,7 +1367,10 @@
       <c r="D40" t="n">
         <v>833</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1307,7 +1391,7 @@
       <c r="D41" t="n">
         <v>323881</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1328,7 +1412,10 @@
       <c r="D42" t="n">
         <v>320647</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1349,7 +1436,10 @@
       <c r="D43" t="n">
         <v>806</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1370,7 +1460,7 @@
       <c r="D44" t="n">
         <v>191942</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1391,7 +1481,10 @@
       <c r="D45" t="n">
         <v>189636</v>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1412,7 +1505,10 @@
       <c r="D46" t="n">
         <v>823</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1433,7 +1529,7 @@
       <c r="D47" t="n">
         <v>37170</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1454,7 +1550,10 @@
       <c r="D48" t="n">
         <v>36729</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1475,7 +1574,10 @@
       <c r="D49" t="n">
         <v>441</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1496,7 +1598,7 @@
       <c r="D50" t="n">
         <v>41936</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1517,7 +1619,10 @@
       <c r="D51" t="n">
         <v>41426</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1538,7 +1643,10 @@
       <c r="D52" t="n">
         <v>510</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1559,7 +1667,7 @@
       <c r="D53" t="n">
         <v>53805</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1580,7 +1688,10 @@
       <c r="D54" t="n">
         <v>53232</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1601,7 +1712,10 @@
       <c r="D55" t="n">
         <v>573</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1622,7 +1736,7 @@
       <c r="D56" t="n">
         <v>61056</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1643,7 +1757,10 @@
       <c r="D57" t="n">
         <v>60372</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1664,7 +1781,10 @@
       <c r="D58" t="n">
         <v>684</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1685,7 +1805,7 @@
       <c r="D59" t="n">
         <v>63634</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1706,7 +1826,10 @@
       <c r="D60" t="n">
         <v>62737</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1727,7 +1850,10 @@
       <c r="D61" t="n">
         <v>894</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1748,7 +1874,7 @@
       <c r="D62" t="n">
         <v>68903</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1769,7 +1895,10 @@
       <c r="D63" t="n">
         <v>67048</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1790,7 +1919,10 @@
       <c r="D64" t="n">
         <v>1854</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1811,7 +1943,7 @@
       <c r="D65" t="n">
         <v>70544</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1832,7 +1964,10 @@
       <c r="D66" t="n">
         <v>68944</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1853,7 +1988,10 @@
       <c r="D67" t="n">
         <v>1595</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1874,7 +2012,7 @@
       <c r="D68" t="n">
         <v>62929</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1895,7 +2033,10 @@
       <c r="D69" t="n">
         <v>61408</v>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1916,7 +2057,10 @@
       <c r="D70" t="n">
         <v>1513</v>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -1937,7 +2081,7 @@
       <c r="D71" t="n">
         <v>62737</v>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -1958,7 +2102,10 @@
       <c r="D72" t="n">
         <v>60990</v>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -1979,7 +2126,10 @@
       <c r="D73" t="n">
         <v>1738</v>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2000,7 +2150,7 @@
       <c r="D74" t="n">
         <v>62337</v>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2021,7 +2171,10 @@
       <c r="D75" t="n">
         <v>60140</v>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2042,7 +2195,10 @@
       <c r="D76" t="n">
         <v>2185</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2063,7 +2219,7 @@
       <c r="D77" t="n">
         <v>60313</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2084,7 +2240,10 @@
       <c r="D78" t="n">
         <v>58779</v>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2105,7 +2264,10 @@
       <c r="D79" t="n">
         <v>1525</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2126,7 +2288,7 @@
       <c r="D80" t="n">
         <v>76431</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2147,7 +2309,10 @@
       <c r="D81" t="n">
         <v>74139</v>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2168,7 +2333,10 @@
       <c r="D82" t="n">
         <v>2265</v>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2189,7 +2357,7 @@
       <c r="D83" t="n">
         <v>71077</v>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2210,7 +2378,10 @@
       <c r="D84" t="n">
         <v>69787</v>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2231,7 +2402,10 @@
       <c r="D85" t="n">
         <v>1256</v>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2252,7 +2426,7 @@
       <c r="D86" t="n">
         <v>71983</v>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2273,7 +2447,10 @@
       <c r="D87" t="n">
         <v>70760</v>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2294,7 +2471,10 @@
       <c r="D88" t="n">
         <v>1184</v>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2315,7 +2495,7 @@
       <c r="D89" t="n">
         <v>79235</v>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2336,7 +2516,10 @@
       <c r="D90" t="n">
         <v>77793</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2357,7 +2540,10 @@
       <c r="D91" t="n">
         <v>1400</v>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2378,7 +2564,7 @@
       <c r="D92" t="n">
         <v>79086</v>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2399,7 +2585,10 @@
       <c r="D93" t="n">
         <v>77550</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2420,7 +2609,10 @@
       <c r="D94" t="n">
         <v>1503</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2441,7 +2633,7 @@
       <c r="D95" t="n">
         <v>97108</v>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2462,7 +2654,10 @@
       <c r="D96" t="n">
         <v>95360</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2483,7 +2678,10 @@
       <c r="D97" t="n">
         <v>1670</v>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2504,7 +2702,7 @@
       <c r="D98" t="n">
         <v>100767</v>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2525,7 +2723,10 @@
       <c r="D99" t="n">
         <v>99306</v>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2546,7 +2747,10 @@
       <c r="D100" t="n">
         <v>1396</v>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2567,7 +2771,7 @@
       <c r="D101" t="n">
         <v>109423</v>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="F101" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2588,7 +2792,10 @@
       <c r="D102" t="n">
         <v>107093</v>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2609,7 +2816,10 @@
       <c r="D103" t="n">
         <v>2249</v>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2630,7 +2840,7 @@
       <c r="D104" t="n">
         <v>119122</v>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2651,7 +2861,10 @@
       <c r="D105" t="n">
         <v>116854</v>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2672,7 +2885,10 @@
       <c r="D106" t="n">
         <v>2152</v>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2693,7 +2909,7 @@
       <c r="D107" t="n">
         <v>140927</v>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2714,7 +2930,10 @@
       <c r="D108" t="n">
         <v>138709</v>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2735,7 +2954,10 @@
       <c r="D109" t="n">
         <v>2117</v>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2756,7 +2978,7 @@
       <c r="D110" t="n">
         <v>123724</v>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2777,7 +2999,10 @@
       <c r="D111" t="n">
         <v>122008</v>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2798,7 +3023,10 @@
       <c r="D112" t="n">
         <v>1635</v>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2819,7 +3047,7 @@
       <c r="D113" t="n">
         <v>256362</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2840,7 +3068,10 @@
       <c r="D114" t="n">
         <v>254203</v>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2861,7 +3092,10 @@
       <c r="D115" t="n">
         <v>2073</v>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2882,7 +3116,7 @@
       <c r="D116" t="n">
         <v>188367</v>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2903,7 +3137,10 @@
       <c r="D117" t="n">
         <v>186188</v>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2924,7 +3161,10 @@
       <c r="D118" t="n">
         <v>2119</v>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -2945,7 +3185,7 @@
       <c r="D119" t="n">
         <v>233332</v>
       </c>
-      <c r="E119" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -2966,7 +3206,10 @@
       <c r="D120" t="n">
         <v>231095</v>
       </c>
-      <c r="E120" t="inlineStr">
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -2987,7 +3230,10 @@
       <c r="D121" t="n">
         <v>2157</v>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3008,7 +3254,7 @@
       <c r="D122" t="n">
         <v>253166</v>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3029,7 +3275,10 @@
       <c r="D123" t="n">
         <v>251098</v>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3050,7 +3299,10 @@
       <c r="D124" t="n">
         <v>1981</v>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3071,7 +3323,7 @@
       <c r="D125" t="n">
         <v>254841</v>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3092,7 +3344,10 @@
       <c r="D126" t="n">
         <v>253099</v>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3113,7 +3368,10 @@
       <c r="D127" t="n">
         <v>1716</v>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3134,7 +3392,7 @@
       <c r="D128" t="n">
         <v>260128</v>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3155,7 +3413,10 @@
       <c r="D129" t="n">
         <v>258656</v>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3176,7 +3437,10 @@
       <c r="D130" t="n">
         <v>1453</v>
       </c>
-      <c r="E130" t="inlineStr">
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3197,7 +3461,7 @@
       <c r="D131" t="n">
         <v>272751</v>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3218,7 +3482,10 @@
       <c r="D132" t="n">
         <v>271077</v>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3239,7 +3506,10 @@
       <c r="D133" t="n">
         <v>1662</v>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E133" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3260,7 +3530,7 @@
       <c r="D134" t="n">
         <v>266715</v>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3281,7 +3551,10 @@
       <c r="D135" t="n">
         <v>265158</v>
       </c>
-      <c r="E135" t="inlineStr">
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3302,7 +3575,10 @@
       <c r="D136" t="n">
         <v>1540</v>
       </c>
-      <c r="E136" t="inlineStr">
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3323,7 +3599,7 @@
       <c r="D137" t="n">
         <v>301561</v>
       </c>
-      <c r="E137" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3344,7 +3620,10 @@
       <c r="D138" t="n">
         <v>299790</v>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3365,7 +3644,10 @@
       <c r="D139" t="n">
         <v>1667</v>
       </c>
-      <c r="E139" t="inlineStr">
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3386,7 +3668,7 @@
       <c r="D140" t="n">
         <v>282115</v>
       </c>
-      <c r="E140" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3407,7 +3689,10 @@
       <c r="D141" t="n">
         <v>280295</v>
       </c>
-      <c r="E141" t="inlineStr">
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3428,7 +3713,10 @@
       <c r="D142" t="n">
         <v>1628</v>
       </c>
-      <c r="E142" t="inlineStr">
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3449,7 +3737,7 @@
       <c r="D143" t="n">
         <v>277310</v>
       </c>
-      <c r="E143" t="inlineStr">
+      <c r="F143" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3470,7 +3758,10 @@
       <c r="D144" t="n">
         <v>274780</v>
       </c>
-      <c r="E144" t="inlineStr">
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3491,7 +3782,10 @@
       <c r="D145" t="n">
         <v>1626</v>
       </c>
-      <c r="E145" t="inlineStr">
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3512,7 +3806,7 @@
       <c r="D146" t="n">
         <v>274214</v>
       </c>
-      <c r="E146" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3533,7 +3827,10 @@
       <c r="D147" t="n">
         <v>271687</v>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3554,7 +3851,10 @@
       <c r="D148" t="n">
         <v>1597</v>
       </c>
-      <c r="E148" t="inlineStr">
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3575,7 +3875,7 @@
       <c r="D149" t="n">
         <v>263006</v>
       </c>
-      <c r="E149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3596,7 +3896,10 @@
       <c r="D150" t="n">
         <v>260576</v>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3617,7 +3920,10 @@
       <c r="D151" t="n">
         <v>1579</v>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E151" t="n">
+        <v>0</v>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3638,7 +3944,7 @@
       <c r="D152" t="n">
         <v>300524</v>
       </c>
-      <c r="E152" t="inlineStr">
+      <c r="F152" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3659,7 +3965,10 @@
       <c r="D153" t="n">
         <v>297718</v>
       </c>
-      <c r="E153" t="inlineStr">
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3680,7 +3989,10 @@
       <c r="D154" t="n">
         <v>1817</v>
       </c>
-      <c r="E154" t="inlineStr">
+      <c r="E154" t="n">
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3701,7 +4013,7 @@
       <c r="D155" t="n">
         <v>279374</v>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="F155" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3722,7 +4034,10 @@
       <c r="D156" t="n">
         <v>276772</v>
       </c>
-      <c r="E156" t="inlineStr">
+      <c r="E156" t="n">
+        <v>0</v>
+      </c>
+      <c r="F156" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3743,7 +4058,10 @@
       <c r="D157" t="n">
         <v>1543</v>
       </c>
-      <c r="E157" t="inlineStr">
+      <c r="E157" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3764,7 +4082,7 @@
       <c r="D158" t="n">
         <v>307326</v>
       </c>
-      <c r="E158" t="inlineStr">
+      <c r="F158" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3785,7 +4103,10 @@
       <c r="D159" t="n">
         <v>304408</v>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E159" t="n">
+        <v>0</v>
+      </c>
+      <c r="F159" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3806,7 +4127,10 @@
       <c r="D160" t="n">
         <v>1753</v>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3827,7 +4151,7 @@
       <c r="D161" t="n">
         <v>290675</v>
       </c>
-      <c r="E161" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3848,7 +4172,10 @@
       <c r="D162" t="n">
         <v>287581</v>
       </c>
-      <c r="E162" t="inlineStr">
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3869,7 +4196,10 @@
       <c r="D163" t="n">
         <v>1841</v>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E163" t="n">
+        <v>0</v>
+      </c>
+      <c r="F163" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3890,7 +4220,7 @@
       <c r="D164" t="n">
         <v>330991</v>
       </c>
-      <c r="E164" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3911,7 +4241,10 @@
       <c r="D165" t="n">
         <v>328074</v>
       </c>
-      <c r="E165" t="inlineStr">
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3932,7 +4265,10 @@
       <c r="D166" t="n">
         <v>1663</v>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E166" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -3953,7 +4289,7 @@
       <c r="D167" t="n">
         <v>357651</v>
       </c>
-      <c r="E167" t="inlineStr">
+      <c r="F167" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -3974,7 +4310,10 @@
       <c r="D168" t="n">
         <v>354853</v>
       </c>
-      <c r="E168" t="inlineStr">
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -3995,7 +4334,10 @@
       <c r="D169" t="n">
         <v>1585</v>
       </c>
-      <c r="E169" t="inlineStr">
+      <c r="E169" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4016,7 +4358,7 @@
       <c r="D170" t="n">
         <v>328622</v>
       </c>
-      <c r="E170" t="inlineStr">
+      <c r="F170" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4037,7 +4379,10 @@
       <c r="D171" t="n">
         <v>325925</v>
       </c>
-      <c r="E171" t="inlineStr">
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4058,7 +4403,10 @@
       <c r="D172" t="n">
         <v>1507</v>
       </c>
-      <c r="E172" t="inlineStr">
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+      <c r="F172" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4079,7 +4427,7 @@
       <c r="D173" t="n">
         <v>338627</v>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="F173" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4100,7 +4448,10 @@
       <c r="D174" t="n">
         <v>335998</v>
       </c>
-      <c r="E174" t="inlineStr">
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+      <c r="F174" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4121,7 +4472,10 @@
       <c r="D175" t="n">
         <v>1322</v>
       </c>
-      <c r="E175" t="inlineStr">
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4142,7 +4496,7 @@
       <c r="D176" t="n">
         <v>327136</v>
       </c>
-      <c r="E176" t="inlineStr">
+      <c r="F176" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4163,7 +4517,10 @@
       <c r="D177" t="n">
         <v>324531</v>
       </c>
-      <c r="E177" t="inlineStr">
+      <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4184,7 +4541,10 @@
       <c r="D178" t="n">
         <v>1177</v>
       </c>
-      <c r="E178" t="inlineStr">
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4205,7 +4565,7 @@
       <c r="D179" t="n">
         <v>314621</v>
       </c>
-      <c r="E179" t="inlineStr">
+      <c r="F179" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4226,7 +4586,10 @@
       <c r="D180" t="n">
         <v>312232</v>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4247,7 +4610,10 @@
       <c r="D181" t="n">
         <v>1089</v>
       </c>
-      <c r="E181" t="inlineStr">
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4268,7 +4634,7 @@
       <c r="D182" t="n">
         <v>294684</v>
       </c>
-      <c r="E182" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4289,7 +4655,10 @@
       <c r="D183" t="n">
         <v>291915</v>
       </c>
-      <c r="E183" t="inlineStr">
+      <c r="E183" t="n">
+        <v>0</v>
+      </c>
+      <c r="F183" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4310,7 +4679,10 @@
       <c r="D184" t="n">
         <v>1459</v>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4331,7 +4703,7 @@
       <c r="D185" t="n">
         <v>302787</v>
       </c>
-      <c r="E185" t="inlineStr">
+      <c r="F185" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4352,7 +4724,10 @@
       <c r="D186" t="n">
         <v>300009</v>
       </c>
-      <c r="E186" t="inlineStr">
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4373,7 +4748,10 @@
       <c r="D187" t="n">
         <v>1510</v>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4394,7 +4772,7 @@
       <c r="D188" t="n">
         <v>326369</v>
       </c>
-      <c r="E188" t="inlineStr">
+      <c r="F188" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4415,7 +4793,10 @@
       <c r="D189" t="n">
         <v>323430</v>
       </c>
-      <c r="E189" t="inlineStr">
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4436,7 +4817,10 @@
       <c r="D190" t="n">
         <v>1578</v>
       </c>
-      <c r="E190" t="inlineStr">
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4457,7 +4841,7 @@
       <c r="D191" t="n">
         <v>295988</v>
       </c>
-      <c r="E191" t="inlineStr">
+      <c r="F191" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4478,7 +4862,10 @@
       <c r="D192" t="n">
         <v>292727</v>
       </c>
-      <c r="E192" t="inlineStr">
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4499,7 +4886,10 @@
       <c r="D193" t="n">
         <v>1640</v>
       </c>
-      <c r="E193" t="inlineStr">
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4520,7 +4910,7 @@
       <c r="D194" t="n">
         <v>318703</v>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="F194" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4541,7 +4931,10 @@
       <c r="D195" t="n">
         <v>315508</v>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E195" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4562,7 +4955,10 @@
       <c r="D196" t="n">
         <v>1538</v>
       </c>
-      <c r="E196" t="inlineStr">
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4583,7 +4979,7 @@
       <c r="D197" t="n">
         <v>310598</v>
       </c>
-      <c r="E197" t="inlineStr">
+      <c r="F197" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4604,7 +5000,10 @@
       <c r="D198" t="n">
         <v>307762</v>
       </c>
-      <c r="E198" t="inlineStr">
+      <c r="E198" t="n">
+        <v>0</v>
+      </c>
+      <c r="F198" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4625,7 +5024,10 @@
       <c r="D199" t="n">
         <v>1319</v>
       </c>
-      <c r="E199" t="inlineStr">
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4646,7 +5048,7 @@
       <c r="D200" t="n">
         <v>340929</v>
       </c>
-      <c r="E200" t="inlineStr">
+      <c r="F200" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4667,7 +5069,10 @@
       <c r="D201" t="n">
         <v>338006</v>
       </c>
-      <c r="E201" t="inlineStr">
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4688,7 +5093,10 @@
       <c r="D202" t="n">
         <v>1405</v>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4709,7 +5117,7 @@
       <c r="D203" t="n">
         <v>356578</v>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="F203" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4730,7 +5138,10 @@
       <c r="D204" t="n">
         <v>353703</v>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4751,7 +5162,10 @@
       <c r="D205" t="n">
         <v>1387</v>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E205" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4772,7 +5186,7 @@
       <c r="D206" t="n">
         <v>333177</v>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="F206" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4793,7 +5207,10 @@
       <c r="D207" t="n">
         <v>330318</v>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E207" t="n">
+        <v>0</v>
+      </c>
+      <c r="F207" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4814,7 +5231,10 @@
       <c r="D208" t="n">
         <v>1416</v>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4835,7 +5255,7 @@
       <c r="D209" t="n">
         <v>349931</v>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="F209" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4856,7 +5276,10 @@
       <c r="D210" t="n">
         <v>346933</v>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4877,7 +5300,10 @@
       <c r="D211" t="n">
         <v>1490</v>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4898,7 +5324,7 @@
       <c r="D212" t="n">
         <v>319781</v>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="F212" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4919,7 +5345,10 @@
       <c r="D213" t="n">
         <v>317027</v>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E213" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -4940,7 +5369,10 @@
       <c r="D214" t="n">
         <v>1327</v>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E214" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -4961,7 +5393,7 @@
       <c r="D215" t="n">
         <v>321083</v>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -4982,7 +5414,10 @@
       <c r="D216" t="n">
         <v>318346</v>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+      <c r="F216" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5003,7 +5438,10 @@
       <c r="D217" t="n">
         <v>1303</v>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5024,7 +5462,7 @@
       <c r="D218" t="n">
         <v>307406</v>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="F218" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5045,7 +5483,10 @@
       <c r="D219" t="n">
         <v>304619</v>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5066,7 +5507,10 @@
       <c r="D220" t="n">
         <v>1440</v>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5087,7 +5531,7 @@
       <c r="D221" t="n">
         <v>276295</v>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="F221" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5108,7 +5552,10 @@
       <c r="D222" t="n">
         <v>273738</v>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5129,7 +5576,10 @@
       <c r="D223" t="n">
         <v>1491</v>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5150,7 +5600,7 @@
       <c r="D224" t="n">
         <v>320571</v>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="F224" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5171,7 +5621,10 @@
       <c r="D225" t="n">
         <v>317779</v>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+      <c r="F225" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5192,7 +5645,10 @@
       <c r="D226" t="n">
         <v>1610</v>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5213,7 +5669,7 @@
       <c r="D227" t="n">
         <v>305910</v>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="F227" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5234,7 +5690,10 @@
       <c r="D228" t="n">
         <v>303248</v>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5255,7 +5714,10 @@
       <c r="D229" t="n">
         <v>1466</v>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5276,7 +5738,7 @@
       <c r="D230" t="n">
         <v>301910</v>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="F230" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5297,7 +5759,10 @@
       <c r="D231" t="n">
         <v>299344</v>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5318,7 +5783,10 @@
       <c r="D232" t="n">
         <v>1273</v>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E232" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5339,7 +5807,7 @@
       <c r="D233" t="n">
         <v>306763</v>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="F233" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5360,7 +5828,10 @@
       <c r="D234" t="n">
         <v>304231</v>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+      <c r="F234" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5381,7 +5852,10 @@
       <c r="D235" t="n">
         <v>1309</v>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5402,7 +5876,7 @@
       <c r="D236" t="n">
         <v>334098</v>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="F236" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5423,7 +5897,10 @@
       <c r="D237" t="n">
         <v>331296</v>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5444,7 +5921,10 @@
       <c r="D238" t="n">
         <v>1419</v>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5465,7 +5945,7 @@
       <c r="D239" t="n">
         <v>343114</v>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="F239" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5486,7 +5966,10 @@
       <c r="D240" t="n">
         <v>340375</v>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5507,7 +5990,10 @@
       <c r="D241" t="n">
         <v>1310</v>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E241" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5528,7 +6014,7 @@
       <c r="D242" t="n">
         <v>325304</v>
       </c>
-      <c r="E242" t="inlineStr">
+      <c r="F242" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5549,7 +6035,10 @@
       <c r="D243" t="n">
         <v>323331</v>
       </c>
-      <c r="E243" t="inlineStr">
+      <c r="E243" t="n">
+        <v>0</v>
+      </c>
+      <c r="F243" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5570,7 +6059,10 @@
       <c r="D244" t="n">
         <v>1512</v>
       </c>
-      <c r="E244" t="inlineStr">
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5591,7 +6083,7 @@
       <c r="D245" t="n">
         <v>343826</v>
       </c>
-      <c r="E245" t="inlineStr">
+      <c r="F245" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5612,7 +6104,10 @@
       <c r="D246" t="n">
         <v>341108</v>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E246" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5633,7 +6128,10 @@
       <c r="D247" t="n">
         <v>1676</v>
       </c>
-      <c r="E247" t="inlineStr">
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5654,7 +6152,7 @@
       <c r="D248" t="n">
         <v>305082</v>
       </c>
-      <c r="E248" t="inlineStr">
+      <c r="F248" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5675,7 +6173,10 @@
       <c r="D249" t="n">
         <v>302866</v>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E249" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5696,7 +6197,10 @@
       <c r="D250" t="n">
         <v>1305</v>
       </c>
-      <c r="E250" t="inlineStr">
+      <c r="E250" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5717,7 +6221,7 @@
       <c r="D251" t="n">
         <v>303003</v>
       </c>
-      <c r="E251" t="inlineStr">
+      <c r="F251" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5738,7 +6242,10 @@
       <c r="D252" t="n">
         <v>300939</v>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+      <c r="F252" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5759,7 +6266,10 @@
       <c r="D253" t="n">
         <v>1189</v>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E253" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5780,7 +6290,7 @@
       <c r="D254" t="n">
         <v>290951</v>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="F254" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5801,7 +6311,10 @@
       <c r="D255" t="n">
         <v>289016</v>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E255" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5822,7 +6335,10 @@
       <c r="D256" t="n">
         <v>1126</v>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5843,7 +6359,7 @@
       <c r="D257" t="n">
         <v>293401</v>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="F257" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5864,7 +6380,10 @@
       <c r="D258" t="n">
         <v>291368</v>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5885,7 +6404,10 @@
       <c r="D259" t="n">
         <v>1299</v>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E259" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5906,7 +6428,7 @@
       <c r="D260" t="n">
         <v>331710</v>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="F260" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5927,7 +6449,10 @@
       <c r="D261" t="n">
         <v>329281</v>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+      <c r="F261" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -5948,7 +6473,10 @@
       <c r="D262" t="n">
         <v>1583</v>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -5969,7 +6497,7 @@
       <c r="D263" t="n">
         <v>324600</v>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="F263" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -5990,7 +6518,10 @@
       <c r="D264" t="n">
         <v>322513</v>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -6011,7 +6542,10 @@
       <c r="D265" t="n">
         <v>1190</v>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -6032,7 +6566,7 @@
       <c r="D266" t="n">
         <v>307181</v>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="F266" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -6053,7 +6587,10 @@
       <c r="D267" t="n">
         <v>304982</v>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -6074,7 +6611,10 @@
       <c r="D268" t="n">
         <v>1189</v>
       </c>
-      <c r="E268" t="inlineStr">
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -6095,7 +6635,7 @@
       <c r="D269" t="n">
         <v>322371</v>
       </c>
-      <c r="E269" t="inlineStr">
+      <c r="F269" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -6116,7 +6656,10 @@
       <c r="D270" t="n">
         <v>320046</v>
       </c>
-      <c r="E270" t="inlineStr">
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -6137,7 +6680,10 @@
       <c r="D271" t="n">
         <v>1402</v>
       </c>
-      <c r="E271" t="inlineStr">
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -6158,7 +6704,10 @@
       <c r="D272" t="n">
         <v>326841</v>
       </c>
-      <c r="E272" t="inlineStr">
+      <c r="E272" t="n">
+        <v>52153</v>
+      </c>
+      <c r="F272" t="inlineStr">
         <is>
           <t>Total vehicles</t>
         </is>
@@ -6179,7 +6728,10 @@
       <c r="D273" t="n">
         <v>324748</v>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E273" t="n">
+        <v>43951</v>
+      </c>
+      <c r="F273" t="inlineStr">
         <is>
           <t>Passenger cars</t>
         </is>
@@ -6200,7 +6752,10 @@
       <c r="D274" t="n">
         <v>1134</v>
       </c>
-      <c r="E274" t="inlineStr">
+      <c r="E274" t="n">
+        <v>8202</v>
+      </c>
+      <c r="F274" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -6217,16 +6772,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6252,17 +6809,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ambassador Bridge (Detroit) YoY %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Blue Water Bridge (Port Huron) YoY %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Detroit-Windsor Tunnel YoY %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge YoY %</t>
         </is>
       </c>
     </row>
@@ -6281,13 +6848,14 @@
       <c r="D2" t="n">
         <v>308890</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n">
         <v>-0.06502145588700764</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.001105108055009823</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>-0.01082396643929932</v>
       </c>
     </row>
@@ -6306,13 +6874,14 @@
       <c r="D3" t="n">
         <v>305193</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n">
         <v>-0.04167469840427664</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>-0.04513827184120952</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.06996287297931195</v>
       </c>
     </row>
@@ -6331,13 +6900,14 @@
       <c r="D4" t="n">
         <v>356068</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n">
         <v>-0.01879810683422422</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>-0.06011931714369693</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.03336312875103026</v>
       </c>
     </row>
@@ -6356,13 +6926,14 @@
       <c r="D5" t="n">
         <v>351274</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n">
         <v>-0.04680616464937016</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>-0.0183049611424342</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.1519748665276193</v>
       </c>
     </row>
@@ -6381,13 +6952,14 @@
       <c r="D6" t="n">
         <v>366710</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n">
         <v>-0.04081304898138313</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>-0.04269013308172407</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.1801146292249816</v>
       </c>
     </row>
@@ -6406,13 +6978,14 @@
       <c r="D7" t="n">
         <v>356824</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n">
         <v>-0.04756244070087032</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>-0.03472284352926872</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.08005751040484298</v>
       </c>
     </row>
@@ -6431,13 +7004,14 @@
       <c r="D8" t="n">
         <v>355661</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n">
         <v>-0.02514508895283216</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.007520019423284529</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.08271814276885985</v>
       </c>
     </row>
@@ -6456,13 +7030,14 @@
       <c r="D9" t="n">
         <v>390049</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n">
         <v>-0.05140813258588387</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>-0.02876227929633765</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1404708090770072</v>
       </c>
     </row>
@@ -6481,13 +7056,14 @@
       <c r="D10" t="n">
         <v>358837</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n">
         <v>-0.02872679548773377</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>-0.05313995528803138</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.1067359590414212</v>
       </c>
     </row>
@@ -6506,13 +7082,14 @@
       <c r="D11" t="n">
         <v>367152</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n">
         <v>-0.02965217022466526</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>-0.05456415307511805</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.08464081346879329</v>
       </c>
     </row>
@@ -6531,13 +7108,14 @@
       <c r="D12" t="n">
         <v>344698</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n">
         <v>-0.02066562118836034</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>-0.03959356885634346</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.06536897152818129</v>
       </c>
     </row>
@@ -6556,13 +7134,14 @@
       <c r="D13" t="n">
         <v>358561</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n">
         <v>-0.01775347743771244</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>-0.01336448306304414</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>0.09715095269131088</v>
       </c>
     </row>
@@ -6581,13 +7160,14 @@
       <c r="D14" t="n">
         <v>334640</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n">
         <v>0.006615239469448915</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>-0.009252107498151899</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.08336300948557739</v>
       </c>
     </row>
@@ -6606,13 +7186,14 @@
       <c r="D15" t="n">
         <v>323881</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n">
         <v>0.08313633801807113</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.0411840918526578</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>0.06123338346554475</v>
       </c>
     </row>
@@ -6631,13 +7212,14 @@
       <c r="D16" t="n">
         <v>191942</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n">
         <v>-0.2934969524745376</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>-0.3619011396131795</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>-0.4609400451599133</v>
       </c>
     </row>
@@ -6656,13 +7238,14 @@
       <c r="D17" t="n">
         <v>37170</v>
       </c>
-      <c r="E17" s="2" t="n">
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n">
         <v>-0.7281723045524202</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>-0.7733674456508182</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>-0.8941851659957754</v>
       </c>
     </row>
@@ -6681,13 +7264,14 @@
       <c r="D18" t="n">
         <v>41936</v>
       </c>
-      <c r="E18" s="2" t="n">
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n">
         <v>-0.681717435451117</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>-0.7684971701410278</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>-0.8856426058738512</v>
       </c>
     </row>
@@ -6706,13 +7290,14 @@
       <c r="D19" t="n">
         <v>53805</v>
       </c>
-      <c r="E19" s="2" t="n">
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n">
         <v>-0.4793316238834568</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>-0.6833399481430605</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>-0.8492113759164182</v>
       </c>
     </row>
@@ -6731,13 +7316,14 @@
       <c r="D20" t="n">
         <v>61056</v>
       </c>
-      <c r="E20" s="2" t="n">
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n">
         <v>-0.4827771112954002</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>-0.6982901256747946</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>-0.828330910614321</v>
       </c>
     </row>
@@ -6756,13 +7342,14 @@
       <c r="D21" t="n">
         <v>63634</v>
       </c>
-      <c r="E21" s="2" t="n">
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n">
         <v>-0.4842046918302822</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>-0.6963633334027619</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>-0.8368563949657607</v>
       </c>
     </row>
@@ -6781,13 +7368,14 @@
       <c r="D22" t="n">
         <v>68903</v>
       </c>
-      <c r="E22" s="2" t="n">
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n">
         <v>-0.4267016612629197</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>-0.6057690327098953</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>-0.8079824544291698</v>
       </c>
     </row>
@@ -6806,13 +7394,14 @@
       <c r="D23" t="n">
         <v>70544</v>
       </c>
-      <c r="E23" s="2" t="n">
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n">
         <v>-0.4465347304070769</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>-0.6001031596472144</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>-0.8078615941081623</v>
       </c>
     </row>
@@ -6831,13 +7420,14 @@
       <c r="D24" t="n">
         <v>62929</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n">
         <v>-0.4397889829905345</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>-0.5894671695840895</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>-0.8174372929346848</v>
       </c>
     </row>
@@ -6856,13 +7446,14 @@
       <c r="D25" t="n">
         <v>62737</v>
       </c>
-      <c r="E25" s="2" t="n">
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n">
         <v>-0.4451917242312151</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>-0.5994924748754924</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>-0.8250311662450741</v>
       </c>
     </row>
@@ -6881,13 +7472,14 @@
       <c r="D26" t="n">
         <v>62337</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n">
         <v>-0.4303606017502656</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>-0.5465520125807207</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>-0.8137192206550323</v>
       </c>
     </row>
@@ -6906,13 +7498,14 @@
       <c r="D27" t="n">
         <v>60313</v>
       </c>
-      <c r="E27" s="2" t="n">
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n">
         <v>-0.4641165568369028</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>-0.5514126313546067</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>-0.8137803699506918</v>
       </c>
     </row>
@@ -6931,13 +7524,14 @@
       <c r="D28" t="n">
         <v>76431</v>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n">
         <v>-0.1629017214198954</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>-0.2718883835930946</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>-0.6018015858957393</v>
       </c>
     </row>
@@ -6956,13 +7550,14 @@
       <c r="D29" t="n">
         <v>71077</v>
       </c>
-      <c r="E29" s="2" t="n">
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n">
         <v>1.057114756627497</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>0.8561679019593454</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.9122141511972021</v>
       </c>
     </row>
@@ -6981,13 +7576,14 @@
       <c r="D30" t="n">
         <v>71983</v>
       </c>
-      <c r="E30" s="2" t="n">
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n">
         <v>0.6502531302735474</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>0.6912592045528596</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>0.7164965661961084</v>
       </c>
     </row>
@@ -7006,13 +7602,14 @@
       <c r="D31" t="n">
         <v>79235</v>
       </c>
-      <c r="E31" s="2" t="n">
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n">
         <v>0.09252338233702399</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>0.2466639648158989</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.4726326549577177</v>
       </c>
     </row>
@@ -7031,13 +7628,14 @@
       <c r="D32" t="n">
         <v>79086</v>
       </c>
-      <c r="E32" s="2" t="n">
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n">
         <v>0.02563839127267293</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>0.1270663072468729</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>0.2953026729559748</v>
       </c>
     </row>
@@ -7056,13 +7654,14 @@
       <c r="D33" t="n">
         <v>97108</v>
       </c>
-      <c r="E33" s="2" t="n">
+      <c r="E33" s="2" t="n"/>
+      <c r="F33" s="2" t="n">
         <v>0.08834159719573548</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>0.2602912628019125</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>0.5260395386114342</v>
       </c>
     </row>
@@ -7081,13 +7680,14 @@
       <c r="D34" t="n">
         <v>100767</v>
       </c>
-      <c r="E34" s="2" t="n">
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n">
         <v>0.07713293276557733</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>0.1823881708280812</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>0.4624472083944096</v>
       </c>
     </row>
@@ -7106,13 +7706,14 @@
       <c r="D35" t="n">
         <v>109423</v>
       </c>
-      <c r="E35" s="2" t="n">
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n">
         <v>0.06622886561750424</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>0.2052231658259371</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>0.5511312088909049</v>
       </c>
     </row>
@@ -7131,13 +7732,14 @@
       <c r="D36" t="n">
         <v>119122</v>
       </c>
-      <c r="E36" s="2" t="n">
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="n">
         <v>0.2306890977288391</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>0.3418080822485247</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.8929587312685725</v>
       </c>
     </row>
@@ -7156,13 +7758,14 @@
       <c r="D37" t="n">
         <v>140927</v>
       </c>
-      <c r="E37" s="2" t="n">
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n">
         <v>0.2925759756200796</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>0.4967817016752392</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>1.246313977397708</v>
       </c>
     </row>
@@ -7181,13 +7784,14 @@
       <c r="D38" t="n">
         <v>123724</v>
       </c>
-      <c r="E38" s="2" t="n">
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n">
         <v>0.03779434584971949</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>0.1852466758164726</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>0.9847602547443733</v>
       </c>
     </row>
@@ -7206,13 +7810,14 @@
       <c r="D39" t="n">
         <v>256362</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n">
         <v>-0.2229938377502985</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>0.3955509237618679</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>3.250526420506358</v>
       </c>
     </row>
@@ -7231,13 +7836,14 @@
       <c r="D40" t="n">
         <v>188367</v>
       </c>
-      <c r="E40" s="2" t="n">
+      <c r="E40" s="2" t="n"/>
+      <c r="F40" s="2" t="n">
         <v>0.0635503788941903</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>0.3842580801649385</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>1.464536640891785</v>
       </c>
     </row>
@@ -7256,13 +7862,14 @@
       <c r="D41" t="n">
         <v>233332</v>
       </c>
-      <c r="E41" s="2" t="n">
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="n">
         <v>0.2068415970601194</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>0.7064059987875912</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>2.282805970989209</v>
       </c>
     </row>
@@ -7281,13 +7888,14 @@
       <c r="D42" t="n">
         <v>253166</v>
       </c>
-      <c r="E42" s="2" t="n">
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n">
         <v>0.2811685319496784</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>0.7899191502751716</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>2.517024853090313</v>
       </c>
     </row>
@@ -7306,13 +7914,14 @@
       <c r="D43" t="n">
         <v>254841</v>
       </c>
-      <c r="E43" s="2" t="n">
+      <c r="E43" s="2" t="n"/>
+      <c r="F43" s="2" t="n">
         <v>0.224123663276902</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>0.7633286777277434</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>2.21626806335584</v>
       </c>
     </row>
@@ -7331,13 +7940,14 @@
       <c r="D44" t="n">
         <v>260128</v>
       </c>
-      <c r="E44" s="2" t="n">
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n">
         <v>0.2968099734999226</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>0.9354293740983524</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>2.289178868573452</v>
       </c>
     </row>
@@ -7356,13 +7966,14 @@
       <c r="D45" t="n">
         <v>272751</v>
       </c>
-      <c r="E45" s="2" t="n">
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n">
         <v>0.3027997040646608</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>0.7244889072739544</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>1.808738723895045</v>
       </c>
     </row>
@@ -7381,13 +7992,14 @@
       <c r="D46" t="n">
         <v>266715</v>
       </c>
-      <c r="E46" s="2" t="n">
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n">
         <v>0.2087374832596478</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>0.5926126414750413</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>1.646848670695763</v>
       </c>
     </row>
@@ -7406,13 +8018,14 @@
       <c r="D47" t="n">
         <v>301561</v>
       </c>
-      <c r="E47" s="2" t="n">
+      <c r="E47" s="2" t="n"/>
+      <c r="F47" s="2" t="n">
         <v>0.2496069969629713</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>0.6347390728476822</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>1.755919687817004</v>
       </c>
     </row>
@@ -7431,13 +8044,14 @@
       <c r="D48" t="n">
         <v>282115</v>
       </c>
-      <c r="E48" s="2" t="n">
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n">
         <v>0.1776198980118504</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>0.506832122107735</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>1.368286294723057</v>
       </c>
     </row>
@@ -7456,13 +8070,14 @@
       <c r="D49" t="n">
         <v>277310</v>
       </c>
-      <c r="E49" s="2" t="n">
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="n">
         <v>0.1136510098760904</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>0.2772199771547049</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>0.9677563561276405</v>
       </c>
     </row>
@@ -7481,13 +8096,14 @@
       <c r="D50" t="n">
         <v>274214</v>
       </c>
-      <c r="E50" s="2" t="n">
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n">
         <v>0.3835153971935016</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>0.6014119668548874</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="H50" s="2" t="n">
         <v>1.216336361578998</v>
       </c>
     </row>
@@ -7506,13 +8122,14 @@
       <c r="D51" t="n">
         <v>263006</v>
       </c>
-      <c r="E51" s="2" t="n">
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n">
         <v>0.8697076746445288</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>0.3102439077960443</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>0.02591647748106194</v>
       </c>
     </row>
@@ -7531,13 +8148,14 @@
       <c r="D52" t="n">
         <v>300524</v>
       </c>
-      <c r="E52" s="2" t="n">
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="n">
         <v>0.3278171123361561</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>0.2884728269916506</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="H52" s="2" t="n">
         <v>0.5954174563485112</v>
       </c>
     </row>
@@ -7556,13 +8174,14 @@
       <c r="D53" t="n">
         <v>279374</v>
       </c>
-      <c r="E53" s="2" t="n">
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n">
         <v>0.2434665527375358</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>0.103976893165644</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>0.1973239847084841</v>
       </c>
     </row>
@@ -7581,13 +8200,14 @@
       <c r="D54" t="n">
         <v>307326</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="2" t="n"/>
+      <c r="F54" s="2" t="n">
         <v>0.3215176090341144</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>0.1582618179730777</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>0.2139307805945506</v>
       </c>
     </row>
@@ -7606,13 +8226,14 @@
       <c r="D55" t="n">
         <v>290675</v>
       </c>
-      <c r="E55" s="2" t="n">
+      <c r="E55" s="2" t="n"/>
+      <c r="F55" s="2" t="n">
         <v>0.3258812635828491</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>0.1846140189755653</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="H55" s="2" t="n">
         <v>0.1406131666411606</v>
       </c>
     </row>
@@ -7631,13 +8252,14 @@
       <c r="D56" t="n">
         <v>330991</v>
       </c>
-      <c r="E56" s="2" t="n">
+      <c r="E56" s="2" t="n"/>
+      <c r="F56" s="2" t="n">
         <v>0.319820136138498</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>0.09281326520270823</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>0.2724158875630459</v>
       </c>
     </row>
@@ -7656,13 +8278,14 @@
       <c r="D57" t="n">
         <v>357651</v>
       </c>
-      <c r="E57" s="2" t="n">
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="n">
         <v>0.2724623510373479</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>0.07779250702269355</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>0.3112729192560247</v>
       </c>
     </row>
@@ -7681,13 +8304,14 @@
       <c r="D58" t="n">
         <v>328622</v>
       </c>
-      <c r="E58" s="2" t="n">
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="n">
         <v>0.2206733499449499</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>0.07283100667649355</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="H58" s="2" t="n">
         <v>0.2321091802110867</v>
       </c>
     </row>
@@ -7706,13 +8330,14 @@
       <c r="D59" t="n">
         <v>338627</v>
       </c>
-      <c r="E59" s="2" t="n">
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="n">
         <v>0.1775916993608982</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>0.02209316268955169</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>0.1229137720063271</v>
       </c>
     </row>
@@ -7731,13 +8356,14 @@
       <c r="D60" t="n">
         <v>327136</v>
       </c>
-      <c r="E60" s="2" t="n">
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n">
         <v>0.1233906684519518</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>0.01479123004997582</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>0.1595838576467044</v>
       </c>
     </row>
@@ -7756,13 +8382,14 @@
       <c r="D61" t="n">
         <v>314621</v>
       </c>
-      <c r="E61" s="2" t="n">
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="n">
         <v>0.1172814821436132</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>0.06986723984382927</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="H61" s="2" t="n">
         <v>0.1345461757599798</v>
       </c>
     </row>
@@ -7781,13 +8408,14 @@
       <c r="D62" t="n">
         <v>294684</v>
       </c>
-      <c r="E62" s="2" t="n">
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="n">
         <v>0.07846274143246182</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>-0.01149554873070793</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>0.07464972612631011</v>
       </c>
     </row>
@@ -7806,13 +8434,14 @@
       <c r="D63" t="n">
         <v>302787</v>
       </c>
-      <c r="E63" s="2" t="n">
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="n">
         <v>0.1378154713826184</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>0.1228611300860367</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>0.1512551044462864</v>
       </c>
     </row>
@@ -7831,13 +8460,14 @@
       <c r="D64" t="n">
         <v>326369</v>
       </c>
-      <c r="E64" s="2" t="n">
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n">
         <v>0.04330371427378982</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>0.06380512018495223</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>0.08599978703863918</v>
       </c>
     </row>
@@ -7856,13 +8486,14 @@
       <c r="D65" t="n">
         <v>295988</v>
       </c>
-      <c r="E65" s="2" t="n">
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n">
         <v>0.1118061441008844</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>0.1169577961370839</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>0.05946866923908452</v>
       </c>
     </row>
@@ -7881,13 +8512,14 @@
       <c r="D66" t="n">
         <v>318703</v>
       </c>
-      <c r="E66" s="2" t="n">
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="n">
         <v>0.04642449029809429</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>0.1279240490645521</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="H66" s="2" t="n">
         <v>0.03701932150224842</v>
       </c>
     </row>
@@ -7906,13 +8538,14 @@
       <c r="D67" t="n">
         <v>310598</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="n">
         <v>-0.04240662678721464</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>-0.006962997547387867</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="H67" s="2" t="n">
         <v>0.0685404661563602</v>
       </c>
     </row>
@@ -7931,13 +8564,14 @@
       <c r="D68" t="n">
         <v>340929</v>
       </c>
-      <c r="E68" s="2" t="n">
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="n">
         <v>-0.03667687636451991</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>0.134426052956715</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="H68" s="2" t="n">
         <v>0.03002498557362587</v>
       </c>
     </row>
@@ -7956,13 +8590,14 @@
       <c r="D69" t="n">
         <v>356578</v>
       </c>
-      <c r="E69" s="2" t="n">
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n">
         <v>-0.03944774499227387</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>0.1614076497099365</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="H69" s="2" t="n">
         <v>-0.003000131413025547</v>
       </c>
     </row>
@@ -7981,13 +8616,14 @@
       <c r="D70" t="n">
         <v>333177</v>
       </c>
-      <c r="E70" s="2" t="n">
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="n">
         <v>-0.02416691826693934</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>0.1120507946360451</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="H70" s="2" t="n">
         <v>0.01386091010340148</v>
       </c>
     </row>
@@ -8006,13 +8642,14 @@
       <c r="D71" t="n">
         <v>349931</v>
       </c>
-      <c r="E71" s="2" t="n">
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n">
         <v>-0.003786544065417163</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>0.1241953997476013</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="H71" s="2" t="n">
         <v>0.03338186263942332</v>
       </c>
     </row>
@@ -8031,13 +8668,14 @@
       <c r="D72" t="n">
         <v>319781</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n">
         <v>-0.06835742808151704</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>0.1312601771317368</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="H72" s="2" t="n">
         <v>-0.02248300401056441</v>
       </c>
     </row>
@@ -8056,13 +8694,14 @@
       <c r="D73" t="n">
         <v>321083</v>
       </c>
-      <c r="E73" s="2" t="n">
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n">
         <v>-0.01107854778808014</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>0.09774789963190873</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="H73" s="2" t="n">
         <v>0.02053899771471071</v>
       </c>
     </row>
@@ -8081,13 +8720,14 @@
       <c r="D74" t="n">
         <v>307406</v>
       </c>
-      <c r="E74" s="2" t="n">
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n">
         <v>-0.06587050911303159</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>0.1607681507670889</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="H74" s="2" t="n">
         <v>0.04317166863487668</v>
       </c>
     </row>
@@ -8106,13 +8746,14 @@
       <c r="D75" t="n">
         <v>276295</v>
       </c>
-      <c r="E75" s="2" t="n">
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="n">
         <v>-0.1722886789672186</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>0.01561940164815478</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="H75" s="2" t="n">
         <v>-0.08749384881121051</v>
       </c>
     </row>
@@ -8131,13 +8772,14 @@
       <c r="D76" t="n">
         <v>320571</v>
       </c>
-      <c r="E76" s="2" t="n">
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n">
         <v>-0.1161716410518215</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>0.02302355088096083</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="H76" s="2" t="n">
         <v>-0.01776516764766262</v>
       </c>
     </row>
@@ -8156,13 +8798,14 @@
       <c r="D77" t="n">
         <v>305910</v>
       </c>
-      <c r="E77" s="2" t="n">
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="n">
         <v>-0.2117690466469136</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>-0.07874464513866272</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="H77" s="2" t="n">
         <v>0.03352162925524008</v>
       </c>
     </row>
@@ -8181,13 +8824,14 @@
       <c r="D78" t="n">
         <v>301910</v>
       </c>
-      <c r="E78" s="2" t="n">
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n">
         <v>-0.1855454310628936</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>-0.1210636597563019</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="H78" s="2" t="n">
         <v>-0.05269169101012541</v>
       </c>
     </row>
@@ -8206,13 +8850,14 @@
       <c r="D79" t="n">
         <v>306763</v>
       </c>
-      <c r="E79" s="2" t="n">
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="n">
         <v>-0.1532140587298998</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>-0.01792425724327477</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="H79" s="2" t="n">
         <v>-0.01234714969188469</v>
       </c>
     </row>
@@ -8231,13 +8876,14 @@
       <c r="D80" t="n">
         <v>334098</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n">
         <v>-0.1121210391724031</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>-0.045001687728107</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="H80" s="2" t="n">
         <v>-0.02003642987249545</v>
       </c>
     </row>
@@ -8256,13 +8902,14 @@
       <c r="D81" t="n">
         <v>343114</v>
       </c>
-      <c r="E81" s="2" t="n">
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n">
         <v>-0.1389880125830325</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>-0.05983953362884965</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="H81" s="2" t="n">
         <v>-0.03775891950709242</v>
       </c>
     </row>
@@ -8281,13 +8928,14 @@
       <c r="D82" t="n">
         <v>325304</v>
       </c>
-      <c r="E82" s="2" t="n">
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n">
         <v>-0.1083689108040054</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>-0.03995243964835574</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="H82" s="2" t="n">
         <v>-0.02363008250869658</v>
       </c>
     </row>
@@ -8306,13 +8954,14 @@
       <c r="D83" t="n">
         <v>343826</v>
       </c>
-      <c r="E83" s="2" t="n">
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="n">
         <v>-0.08879519109484188</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>-0.0753281698642192</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="H83" s="2" t="n">
         <v>-0.01744629655560668</v>
       </c>
     </row>
@@ -8331,13 +8980,14 @@
       <c r="D84" t="n">
         <v>305082</v>
       </c>
-      <c r="E84" s="2" t="n">
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n">
         <v>-0.102590732159795</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>-0.1411172354070121</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="H84" s="2" t="n">
         <v>-0.04596583286686826</v>
       </c>
     </row>
@@ -8356,13 +9006,14 @@
       <c r="D85" t="n">
         <v>303003</v>
       </c>
-      <c r="E85" s="2" t="n">
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="n">
         <v>-0.1134487236805689</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="G85" s="2" t="n">
         <v>-0.1211773137690294</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="H85" s="2" t="n">
         <v>-0.05630942778035586</v>
       </c>
     </row>
@@ -8381,13 +9032,14 @@
       <c r="D86" t="n">
         <v>290951</v>
       </c>
-      <c r="E86" s="2" t="n">
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n">
         <v>-0.1459465246366727</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="G86" s="2" t="n">
         <v>-0.1730430422290887</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="H86" s="2" t="n">
         <v>-0.05352855832352003</v>
       </c>
     </row>
@@ -8406,13 +9058,14 @@
       <c r="D87" t="n">
         <v>293401</v>
       </c>
-      <c r="E87" s="2" t="n">
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n">
         <v>-0.03464455166464375</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="G87" s="2" t="n">
         <v>-0.09570374943499399</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="H87" s="2" t="n">
         <v>0.06191208671890552</v>
       </c>
     </row>
@@ -8431,13 +9084,14 @@
       <c r="D88" t="n">
         <v>331710</v>
       </c>
-      <c r="E88" s="2" t="n">
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n">
         <v>-0.01067308086065724</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="G88" s="2" t="n">
         <v>-0.06230533487867892</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="H88" s="2" t="n">
         <v>0.03474737265691532</v>
       </c>
     </row>
@@ -8456,13 +9110,14 @@
       <c r="D89" t="n">
         <v>324600</v>
       </c>
-      <c r="E89" s="2" t="n">
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n">
         <v>0.08821761310849054</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="G89" s="2" t="n">
         <v>0.009150548964954621</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="H89" s="2" t="n">
         <v>0.06109640090222614</v>
       </c>
     </row>
@@ -8481,13 +9136,14 @@
       <c r="D90" t="n">
         <v>307181</v>
       </c>
-      <c r="E90" s="2" t="n">
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n">
         <v>0.1652114000743673</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="G90" s="2" t="n">
         <v>-0.02749839871272125</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="H90" s="2" t="n">
         <v>0.01745884535126362</v>
       </c>
     </row>
@@ -8506,13 +9162,14 @@
       <c r="D91" t="n">
         <v>322371</v>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="n">
         <v>0.1862097824065464</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="G91" s="2" t="n">
         <v>-0.03109180371470367</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="H91" s="2" t="n">
         <v>0.05087966932126756</v>
       </c>
     </row>
@@ -8532,12 +9189,15 @@
         <v>326841</v>
       </c>
       <c r="E92" s="2" t="n">
+        <v>52153</v>
+      </c>
+      <c r="F92" s="2" t="n">
         <v>0.07100067805326139</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="G92" s="2" t="n">
         <v>-0.03053213785714483</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="H92" s="2" t="n">
         <v>-0.02172117163227556</v>
       </c>
     </row>
@@ -8552,16 +9212,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8587,17 +9249,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ambassador Bridge (Detroit) YoY %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Blue Water Bridge (Port Huron) YoY %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Detroit-Windsor Tunnel YoY %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge YoY %</t>
         </is>
       </c>
     </row>
@@ -8617,12 +9289,15 @@
         <v>305531</v>
       </c>
       <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>-0.080884266719829</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>-0.06142504798831874</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>-0.001604459810079014</v>
       </c>
     </row>
@@ -8642,12 +9317,15 @@
         <v>301919</v>
       </c>
       <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>-0.030971935944189</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>-0.06487974500144886</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.08190265280599721</v>
       </c>
     </row>
@@ -8667,12 +9345,15 @@
         <v>352582</v>
       </c>
       <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>-0.02822559823189813</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>-0.07296155596867303</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.04116441551845312</v>
       </c>
     </row>
@@ -8692,12 +9373,15 @@
         <v>347738</v>
       </c>
       <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>-0.04002598467543117</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>-0.01693599666717828</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.1599579698784129</v>
       </c>
     </row>
@@ -8717,12 +9401,15 @@
         <v>363015</v>
       </c>
       <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>-0.0708423747775617</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>-0.04861455282721334</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.1864437246910635</v>
       </c>
     </row>
@@ -8742,12 +9429,15 @@
         <v>353264</v>
       </c>
       <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>-0.06972197239275799</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>-0.02748085816086726</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.08030482807549755</v>
       </c>
     </row>
@@ -8767,12 +9457,15 @@
         <v>352049</v>
       </c>
       <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>-0.03435270295230299</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.01705947339348186</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.08230523523028066</v>
       </c>
     </row>
@@ -8792,12 +9485,15 @@
         <v>386184</v>
       </c>
       <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>-0.06396030832719365</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>-0.01623700491838253</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1404204551830448</v>
       </c>
     </row>
@@ -8817,12 +9513,15 @@
         <v>355165</v>
       </c>
       <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>-0.05099077643028005</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>-0.05140777999345219</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.1061642342359178</v>
       </c>
     </row>
@@ -8842,12 +9541,15 @@
         <v>363343</v>
       </c>
       <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>-0.03079526392958276</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>-0.02692542716366421</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.08430171832381361</v>
       </c>
     </row>
@@ -8867,12 +9569,15 @@
         <v>341197</v>
       </c>
       <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>-0.02593208237577813</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>-0.02506974665584852</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>0.06542158215871549</v>
       </c>
     </row>
@@ -8892,12 +9597,15 @@
         <v>355306</v>
       </c>
       <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>-0.03917727717923605</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>-0.003514299563742123</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>0.09684350255452483</v>
       </c>
     </row>
@@ -8917,12 +9625,15 @@
         <v>331282</v>
       </c>
       <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>0.02629945834563453</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>0.0260626365622724</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.0842827732701428</v>
       </c>
     </row>
@@ -8942,12 +9653,15 @@
         <v>320647</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>0.1045935146915895</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.06153512441510954</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>0.06202988218694418</v>
       </c>
     </row>
@@ -8967,12 +9681,15 @@
         <v>189636</v>
       </c>
       <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>-0.3819558101472995</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>-0.5187226387907378</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>-0.4621506486434361</v>
       </c>
     </row>
@@ -8992,12 +9709,15 @@
         <v>36729</v>
       </c>
       <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>-0.8556182953751262</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>-0.9698357964607691</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>-0.8943773760704898</v>
       </c>
     </row>
@@ -9017,12 +9737,15 @@
         <v>41426</v>
       </c>
       <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>-0.8180307291161608</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>-0.9666327271579214</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>-0.8858835034364971</v>
       </c>
     </row>
@@ -9042,12 +9765,15 @@
         <v>53232</v>
       </c>
       <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>-0.70536464901219</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>-0.9554684704156583</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>-0.8493138276190045</v>
       </c>
     </row>
@@ -9067,12 +9793,15 @@
         <v>60372</v>
       </c>
       <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>-0.716813783136627</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>-0.9583065545427389</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>-0.8285125082019833</v>
       </c>
     </row>
@@ -9092,12 +9821,15 @@
         <v>62737</v>
       </c>
       <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
         <v>-0.717155575847506</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>-0.9560237962664478</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>-0.8375463509622356</v>
       </c>
     </row>
@@ -9117,12 +9849,15 @@
         <v>67048</v>
       </c>
       <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>-0.6701898152479596</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>-0.943680532132688</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>-0.811220137119367</v>
       </c>
     </row>
@@ -9142,12 +9877,15 @@
         <v>68944</v>
       </c>
       <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
         <v>-0.6732339332140667</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>-0.9412052272618877</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>-0.8102509199296533</v>
       </c>
     </row>
@@ -9167,12 +9905,15 @@
         <v>61408</v>
       </c>
       <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>-0.6690317075824471</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>-0.9421448248545833</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>-0.8200218642016196</v>
       </c>
     </row>
@@ -9192,12 +9933,15 @@
         <v>60990</v>
       </c>
       <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>-0.6819485233602758</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>-0.9425261896075467</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>-0.8283451447484703</v>
       </c>
     </row>
@@ -9217,12 +9961,15 @@
         <v>60140</v>
       </c>
       <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>-0.6525584426258381</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>-0.9327874251837045</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>-0.818462820195483</v>
       </c>
     </row>
@@ -9242,12 +9989,15 @@
         <v>58779</v>
       </c>
       <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>-0.6695877586692145</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>-0.9391828775600757</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>-0.8166862624630824</v>
       </c>
     </row>
@@ -9267,12 +10017,15 @@
         <v>74139</v>
       </c>
       <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
         <v>-0.4055292605441563</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>-0.879766206771613</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>-0.6090457508068088</v>
       </c>
     </row>
@@ -9292,12 +10045,15 @@
         <v>69787</v>
       </c>
       <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>1.610084517864003</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>1.337326234841763</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>0.9000517302404095</v>
       </c>
     </row>
@@ -9317,12 +10073,15 @@
         <v>70760</v>
       </c>
       <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>0.9911775590259788</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>1.012063867534003</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>0.7081060203736783</v>
       </c>
     </row>
@@ -9342,12 +10101,15 @@
         <v>77793</v>
       </c>
       <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
         <v>0.3014712438698172</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>0.4317313812858052</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>0.4613954012623985</v>
       </c>
     </row>
@@ -9367,12 +10129,15 @@
         <v>77550</v>
       </c>
       <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>0.2038158136121813</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>0.738674193081488</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>0.2845358775591334</v>
       </c>
     </row>
@@ -9392,12 +10157,15 @@
         <v>95360</v>
       </c>
       <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>0.373780938929244</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>1.781554045048647</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>0.5199961745062722</v>
       </c>
     </row>
@@ -9417,12 +10185,15 @@
         <v>99306</v>
       </c>
       <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
         <v>0.4234032789620792</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>1.903551532033426</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>0.4811180050113352</v>
       </c>
     </row>
@@ -9442,12 +10213,15 @@
         <v>107093</v>
       </c>
       <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
         <v>0.3046768977844641</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>1.898262691813696</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>0.5533331399396612</v>
       </c>
     </row>
@@ -9467,12 +10241,15 @@
         <v>116854</v>
       </c>
       <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
         <v>0.6063568413038964</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>3.135923076923077</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.902911672746222</v>
       </c>
     </row>
@@ -9492,12 +10269,15 @@
         <v>138709</v>
       </c>
       <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
         <v>0.7871780205013664</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>4.535328345802161</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>1.274290867355304</v>
       </c>
     </row>
@@ -9517,12 +10297,15 @@
         <v>122008</v>
       </c>
       <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
         <v>0.2144721835001901</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>1.969753295032106</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>1.028732956434985</v>
       </c>
     </row>
@@ -9542,12 +10325,15 @@
         <v>254203</v>
       </c>
       <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
         <v>-0.1968277309040698</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>2.315349908802918</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>3.324724816686231</v>
       </c>
     </row>
@@ -9567,12 +10353,15 @@
         <v>186188</v>
       </c>
       <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
         <v>0.1860518932052877</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>4.009357652656622</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>1.511336813283157</v>
       </c>
     </row>
@@ -9592,12 +10381,15 @@
         <v>231095</v>
       </c>
       <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
         <v>0.4095421729307261</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>5.960835178740905</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>2.311433361514322</v>
       </c>
     </row>
@@ -9617,12 +10409,15 @@
         <v>251098</v>
       </c>
       <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
         <v>0.5477868474656913</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>6.441041617681637</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>2.548586772187677</v>
       </c>
     </row>
@@ -9642,12 +10437,15 @@
         <v>253099</v>
       </c>
       <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n">
         <v>0.5131542888462592</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>6.812326330999222</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>2.253493244893499</v>
       </c>
     </row>
@@ -9667,12 +10465,15 @@
         <v>258656</v>
       </c>
       <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
         <v>0.6957759552242941</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>6.066056191467221</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>2.335344938749194</v>
       </c>
     </row>
@@ -9692,12 +10493,15 @@
         <v>271077</v>
       </c>
       <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>0.5820762164709338</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>3.033397220891231</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>1.842669882550336</v>
       </c>
     </row>
@@ -9717,12 +10521,15 @@
         <v>265158</v>
       </c>
       <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
         <v>0.3614846250337042</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>2.430819043050726</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>1.670110567337321</v>
       </c>
     </row>
@@ -9742,12 +10549,15 @@
         <v>299790</v>
       </c>
       <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
         <v>0.5169517718524507</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>2.814689555441527</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>1.799342627435967</v>
       </c>
     </row>
@@ -9767,12 +10577,15 @@
         <v>280295</v>
       </c>
       <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
         <v>0.3418371193761377</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>1.901984488626853</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>1.398676981532511</v>
       </c>
     </row>
@@ -9792,12 +10605,15 @@
         <v>274780</v>
       </c>
       <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n">
         <v>0.2314695333218179</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>0.9775833117175661</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>0.9809817675853766</v>
       </c>
     </row>
@@ -9817,12 +10633,15 @@
         <v>271687</v>
       </c>
       <c r="E50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n">
         <v>0.6799257048646619</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>2.628819345661451</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="H50" s="2" t="n">
         <v>1.22679660350141</v>
       </c>
     </row>
@@ -9842,12 +10661,15 @@
         <v>260576</v>
       </c>
       <c r="E51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n">
         <v>1.596548221083537</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>2.368919388464211</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>0.02507051451005692</v>
       </c>
     </row>
@@ -9867,12 +10689,15 @@
         <v>297718</v>
       </c>
       <c r="E52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="n">
         <v>0.6917847474575031</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>1.313639817629179</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="H52" s="2" t="n">
         <v>0.599018196661439</v>
       </c>
     </row>
@@ -9892,12 +10717,15 @@
         <v>276772</v>
       </c>
       <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n">
         <v>0.4436119667937138</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>0.3889070680628272</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>0.1976546441939462</v>
       </c>
     </row>
@@ -9917,12 +10745,15 @@
         <v>304408</v>
       </c>
       <c r="E54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n">
         <v>0.482639205759874</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>0.3767211483011684</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>0.2123075452612128</v>
       </c>
     </row>
@@ -9942,12 +10773,15 @@
         <v>287581</v>
       </c>
       <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
         <v>0.4907860182921308</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>0.4113178018851147</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="H55" s="2" t="n">
         <v>0.1362391791354371</v>
       </c>
     </row>
@@ -9967,12 +10801,15 @@
         <v>328074</v>
       </c>
       <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n">
         <v>0.42248038266567</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>0.2439886429236225</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>0.2683796239020166</v>
       </c>
     </row>
@@ -9992,12 +10829,15 @@
         <v>354853</v>
       </c>
       <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n">
         <v>0.3558000278512742</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>0.2137579148698576</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>0.3090487204742564</v>
       </c>
     </row>
@@ -10017,12 +10857,15 @@
         <v>325925</v>
       </c>
       <c r="E58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n">
         <v>0.3178084314941104</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>0.2234984061294111</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="H58" s="2" t="n">
         <v>0.2291727950882116</v>
       </c>
     </row>
@@ -10042,12 +10885,15 @@
         <v>335998</v>
       </c>
       <c r="E59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2" t="n">
         <v>0.2610779146993711</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>0.07119491779322658</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>0.1207778778478268</v>
       </c>
     </row>
@@ -10067,12 +10913,15 @@
         <v>324531</v>
       </c>
       <c r="E60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="n">
         <v>0.1995946298488892</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>0.04822118681544052</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>0.1578194402326121</v>
       </c>
     </row>
@@ -10092,12 +10941,15 @@
         <v>312232</v>
       </c>
       <c r="E61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n">
         <v>0.2284488448844884</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>0.136273264483349</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="H61" s="2" t="n">
         <v>0.136298129412621</v>
       </c>
     </row>
@@ -10117,12 +10969,15 @@
         <v>291915</v>
       </c>
       <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n">
         <v>0.1295783279708146</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>-0.02217901578167507</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>0.0744533231255084</v>
       </c>
     </row>
@@ -10142,12 +10997,15 @@
         <v>300009</v>
       </c>
       <c r="E63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="n">
         <v>0.1926643765235972</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>0.1343801837574883</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>0.1513301301731549</v>
       </c>
     </row>
@@ -10167,12 +11025,15 @@
         <v>323430</v>
       </c>
       <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n">
         <v>0.1502344372245228</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>0.1528245340339929</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>0.08636360582833419</v>
       </c>
     </row>
@@ -10192,12 +11053,15 @@
         <v>292727</v>
       </c>
       <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n">
         <v>0.1808206296678059</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>0.07725684218792948</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>0.05764672727009958</v>
       </c>
     </row>
@@ -10217,12 +11081,15 @@
         <v>315508</v>
       </c>
       <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n">
         <v>0.149045625947571</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>0.1536479701621001</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="H66" s="2" t="n">
         <v>0.03646421907440014</v>
       </c>
     </row>
@@ -10242,12 +11109,15 @@
         <v>307762</v>
       </c>
       <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="n">
         <v>0.02346813260239024</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>-0.0190225609387286</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="H67" s="2" t="n">
         <v>0.07017501156195993</v>
       </c>
     </row>
@@ -10267,12 +11137,15 @@
         <v>338006</v>
       </c>
       <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n">
         <v>0.05019584419761311</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>0.060085613357199</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="H68" s="2" t="n">
         <v>0.03027365777233185</v>
       </c>
     </row>
@@ -10292,12 +11165,15 @@
         <v>353703</v>
       </c>
       <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="n">
         <v>0.09925077604309322</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>0.1301647735892454</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="H69" s="2" t="n">
         <v>-0.003240778575917352</v>
       </c>
     </row>
@@ -10317,12 +11193,15 @@
         <v>330318</v>
       </c>
       <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
         <v>0.08363226502009213</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>0.01950073991966586</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="H70" s="2" t="n">
         <v>0.01347856101863926</v>
       </c>
     </row>
@@ -10342,12 +11221,15 @@
         <v>346933</v>
       </c>
       <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
         <v>0.08088961801606979</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>0.01098204857444562</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="H71" s="2" t="n">
         <v>0.03254483657640819</v>
       </c>
     </row>
@@ -10367,12 +11249,15 @@
         <v>317027</v>
       </c>
       <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
         <v>0.0395168710373555</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>0.04743969918376081</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="H72" s="2" t="n">
         <v>-0.02312259845746631</v>
       </c>
     </row>
@@ -10392,12 +11277,15 @@
         <v>318346</v>
       </c>
       <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n">
         <v>0.06534777819569072</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>-0.005771707696420326</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="H73" s="2" t="n">
         <v>0.01958159317430629</v>
       </c>
     </row>
@@ -10417,12 +11305,15 @@
         <v>304619</v>
       </c>
       <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n">
         <v>0.02681618722574354</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>0.01080786376318912</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="H74" s="2" t="n">
         <v>0.04351951766781426</v>
       </c>
     </row>
@@ -10442,12 +11333,15 @@
         <v>273738</v>
       </c>
       <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
         <v>-0.1170066653929482</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>-0.2129424778761062</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="H75" s="2" t="n">
         <v>-0.08756737297881063</v>
       </c>
     </row>
@@ -10467,12 +11361,15 @@
         <v>317779</v>
       </c>
       <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="n">
         <v>-0.09354898342205609</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>-0.2573019236362126</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="H76" s="2" t="n">
         <v>-0.01747209597130755</v>
       </c>
     </row>
@@ -10492,12 +11389,15 @@
         <v>303248</v>
       </c>
       <c r="E77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="n">
         <v>-0.1739649791265303</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>-0.309324633824807</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="H77" s="2" t="n">
         <v>0.03594133783354456</v>
       </c>
     </row>
@@ -10517,12 +11417,15 @@
         <v>299344</v>
       </c>
       <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n">
         <v>-0.1394195527387141</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>-0.3229313809362752</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="H78" s="2" t="n">
         <v>-0.05123166449028234</v>
       </c>
     </row>
@@ -10542,12 +11445,15 @@
         <v>304231</v>
       </c>
       <c r="E79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n">
         <v>-0.09826637624561549</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>-0.1908417342335399</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="H79" s="2" t="n">
         <v>-0.01147315133122348</v>
       </c>
     </row>
@@ -10567,12 +11473,15 @@
         <v>331296</v>
       </c>
       <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
         <v>-0.09822102396395017</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>-0.1853701462002671</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="H80" s="2" t="n">
         <v>-0.01985171860854541</v>
       </c>
     </row>
@@ -10592,12 +11501,15 @@
         <v>340375</v>
       </c>
       <c r="E81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2" t="n">
         <v>-0.1049228748737941</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>-0.1694733241245524</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="H81" s="2" t="n">
         <v>-0.03768133151259673</v>
       </c>
     </row>
@@ -10617,12 +11529,15 @@
         <v>323331</v>
       </c>
       <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
         <v>-0.09770296874481819</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>-0.1908738342898135</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="H82" s="2" t="n">
         <v>-0.02115234410477176</v>
       </c>
     </row>
@@ -10642,12 +11557,15 @@
         <v>341108</v>
       </c>
       <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
         <v>-0.08073473611590204</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>-0.2086111597287699</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="H83" s="2" t="n">
         <v>-0.01678998538622731</v>
       </c>
     </row>
@@ -10667,12 +11585,15 @@
         <v>302866</v>
       </c>
       <c r="E84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n">
         <v>-0.08437829904472539</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>-0.2734394153425873</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="H84" s="2" t="n">
         <v>-0.04466811975005283</v>
       </c>
     </row>
@@ -10692,12 +11613,15 @@
         <v>300939</v>
       </c>
       <c r="E85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n">
         <v>-0.130133812473403</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="G85" s="2" t="n">
         <v>-0.2648399594246116</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="H85" s="2" t="n">
         <v>-0.05467949966388772</v>
       </c>
     </row>
@@ -10717,12 +11641,15 @@
         <v>289016</v>
       </c>
       <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
         <v>-0.1254203885782833</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="G86" s="2" t="n">
         <v>-0.2250222095310616</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="H86" s="2" t="n">
         <v>-0.0512213617666659</v>
       </c>
     </row>
@@ -10742,12 +11669,15 @@
         <v>291368</v>
       </c>
       <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
         <v>-0.03688991406234052</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="G87" s="2" t="n">
         <v>-0.1085204901856968</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="H87" s="2" t="n">
         <v>0.06440464970153943</v>
       </c>
     </row>
@@ -10767,12 +11697,15 @@
         <v>329281</v>
       </c>
       <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="n">
         <v>-0.009799448327353423</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="G88" s="2" t="n">
         <v>-0.0474618802544513</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="H88" s="2" t="n">
         <v>0.03619496568369842</v>
       </c>
     </row>
@@ -10792,12 +11725,15 @@
         <v>322513</v>
       </c>
       <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
         <v>0.0651073628162392</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="G89" s="2" t="n">
         <v>0.09834638050840004</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="H89" s="2" t="n">
         <v>0.06352886086635361</v>
       </c>
     </row>
@@ -10817,12 +11753,15 @@
         <v>304982</v>
       </c>
       <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
         <v>0.1295500932050413</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="G90" s="2" t="n">
         <v>0.1544671848140693</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="H90" s="2" t="n">
         <v>0.01883451814634668</v>
       </c>
     </row>
@@ -10842,12 +11781,15 @@
         <v>320046</v>
       </c>
       <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
         <v>0.1033507970566167</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="G91" s="2" t="n">
         <v>0.1297752095504191</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="H91" s="2" t="n">
         <v>0.05198352567621314</v>
       </c>
     </row>
@@ -10867,12 +11809,15 @@
         <v>324748</v>
       </c>
       <c r="E92" s="2" t="n">
+        <v>43951</v>
+      </c>
+      <c r="F92" s="2" t="n">
         <v>0.009599902970026835</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="G92" s="2" t="n">
         <v>0.1415513346347027</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="H92" s="2" t="n">
         <v>-0.01976480247271322</v>
       </c>
     </row>
@@ -10887,16 +11832,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10922,17 +11869,27 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Ambassador Bridge (Detroit) YoY %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Blue Water Bridge (Port Huron) YoY %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Detroit-Windsor Tunnel YoY %</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge YoY %</t>
         </is>
       </c>
     </row>
@@ -10952,12 +11909,15 @@
         <v>818</v>
       </c>
       <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>-0.03862122992557775</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.09873512030749954</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>-0.7217687074829932</v>
       </c>
     </row>
@@ -10977,12 +11937,15 @@
         <v>834</v>
       </c>
       <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>-0.05785353741137896</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>-0.01658330480381433</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>-0.7676880222841226</v>
       </c>
     </row>
@@ -11002,12 +11965,15 @@
         <v>895</v>
       </c>
       <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>-0.002690899466231417</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>-0.03912453318517164</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>-0.7033476963871396</v>
       </c>
     </row>
@@ -11027,12 +11993,15 @@
         <v>980</v>
       </c>
       <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
         <v>-0.05813555174944948</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>-0.02062715765247411</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>-0.6217676572751833</v>
       </c>
     </row>
@@ -11052,12 +12021,15 @@
         <v>1057</v>
       </c>
       <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>0.01150242213627623</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>-0.03239868683063344</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>-0.4787968441814596</v>
       </c>
     </row>
@@ -11077,12 +12049,15 @@
         <v>969</v>
       </c>
       <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>-0.007134162382453527</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>-0.04928229005951069</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>0.1535714285714286</v>
       </c>
     </row>
@@ -11102,12 +12077,15 @@
         <v>964</v>
       </c>
       <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
         <v>-0.00480139457084702</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>-0.01523357907605676</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>0.220253164556962</v>
       </c>
     </row>
@@ -11127,12 +12105,15 @@
         <v>1009</v>
       </c>
       <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
         <v>-0.02644718088543834</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>-0.05782884839243289</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>0.1286353467561521</v>
       </c>
     </row>
@@ -11152,12 +12133,15 @@
         <v>928</v>
       </c>
       <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
         <v>0.01145849535956862</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>-0.05635142617806994</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -11177,12 +12161,15 @@
         <v>1019</v>
       </c>
       <c r="E11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="n">
         <v>-0.02762300871066468</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>-0.1008484082674678</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>0.04085801838610827</v>
       </c>
     </row>
@@ -11202,12 +12189,15 @@
         <v>916</v>
       </c>
       <c r="E12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2" t="n">
         <v>-0.01189702249382395</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>-0.06268415883260839</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>-0.08308308308308308</v>
       </c>
     </row>
@@ -11227,12 +12217,15 @@
         <v>757</v>
       </c>
       <c r="E13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2" t="n">
         <v>0.02478664969781113</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>-0.03250681874535086</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>0.03556771545827633</v>
       </c>
     </row>
@@ -11252,12 +12245,15 @@
         <v>833</v>
       </c>
       <c r="E14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2" t="n">
         <v>-0.02470473195797224</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>-0.05546480088768339</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>0.01833740831295844</v>
       </c>
     </row>
@@ -11277,12 +12273,15 @@
         <v>806</v>
       </c>
       <c r="E15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2" t="n">
         <v>0.04977511396939108</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.01395905682966385</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>-0.03357314148681055</v>
       </c>
     </row>
@@ -11302,12 +12301,15 @@
         <v>823</v>
       </c>
       <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2" t="n">
         <v>-0.1462314225053079</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>-0.1106320997774915</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>-0.08044692737430167</v>
       </c>
     </row>
@@ -11327,12 +12329,15 @@
         <v>441</v>
       </c>
       <c r="E17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n">
         <v>-0.5111209775313272</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>-0.4496005052433687</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>-0.55</v>
       </c>
     </row>
@@ -11352,12 +12357,15 @@
         <v>510</v>
       </c>
       <c r="E18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>-0.4635724477435652</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>-0.4192391122976806</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>-0.5175023651844843</v>
       </c>
     </row>
@@ -11377,12 +12385,15 @@
         <v>573</v>
       </c>
       <c r="E19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>-0.09294795507313415</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>-0.1261401589521043</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>-0.4086687306501548</v>
       </c>
     </row>
@@ -11402,12 +12413,15 @@
         <v>684</v>
       </c>
       <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="n">
         <v>0.01895904946565349</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>-0.04925174367424328</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>-0.2904564315352697</v>
       </c>
     </row>
@@ -11427,12 +12441,15 @@
         <v>894</v>
       </c>
       <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
         <v>-0.03881389607496352</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>-0.05559087887633305</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>-0.1139742319127849</v>
       </c>
     </row>
@@ -11452,12 +12469,15 @@
         <v>1854</v>
       </c>
       <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
         <v>-0.0143530859134714</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>0.0433919114106885</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>0.9978448275862069</v>
       </c>
     </row>
@@ -11477,12 +12497,15 @@
         <v>1595</v>
       </c>
       <c r="E23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="2" t="n">
         <v>-0.0454227530734673</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>0.01608936624818063</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>0.5652600588812562</v>
       </c>
     </row>
@@ -11502,12 +12525,15 @@
         <v>1513</v>
       </c>
       <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="n">
         <v>-0.06352391604710836</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>0.004618090640320347</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>0.6517467248908297</v>
       </c>
     </row>
@@ -11527,12 +12553,15 @@
         <v>1738</v>
       </c>
       <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="n">
         <v>-0.004419164767106791</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>0.07585193538190796</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>1.295904887714663</v>
       </c>
     </row>
@@ -11552,12 +12581,15 @@
         <v>2185</v>
       </c>
       <c r="E26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="n">
         <v>-0.05832800904310217</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>0.008875981008011225</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>1.623049219687875</v>
       </c>
     </row>
@@ -11577,12 +12609,15 @@
         <v>1525</v>
       </c>
       <c r="E27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="2" t="n">
         <v>-0.1279716178687229</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>0.005443111114832896</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>0.892059553349876</v>
       </c>
     </row>
@@ -11602,12 +12637,15 @@
         <v>2265</v>
       </c>
       <c r="E28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="n">
         <v>0.1294995337270749</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>0.2532158111744809</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>1.752126366950182</v>
       </c>
     </row>
@@ -11627,12 +12665,15 @@
         <v>1256</v>
       </c>
       <c r="E29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="n">
         <v>0.7789843870768279</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>0.8136866402487024</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>1.848072562358277</v>
       </c>
     </row>
@@ -11652,12 +12693,15 @@
         <v>1184</v>
       </c>
       <c r="E30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="n">
         <v>0.4651762682717111</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>0.6599746205047168</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>1.32156862745098</v>
       </c>
     </row>
@@ -11677,12 +12721,15 @@
         <v>1400</v>
       </c>
       <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
         <v>-0.0234978413276825</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>0.2270307914241655</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>1.443280977312391</v>
       </c>
     </row>
@@ -11702,12 +12749,15 @@
         <v>1503</v>
       </c>
       <c r="E32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="n">
         <v>-0.0805212742701564</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>0.06010461923189541</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>1.197368421052632</v>
       </c>
     </row>
@@ -11727,12 +12777,15 @@
         <v>1670</v>
       </c>
       <c r="E33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="n">
         <v>-0.0722529681661227</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>0.08587713258358197</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>0.8680089485458613</v>
       </c>
     </row>
@@ -11752,12 +12805,15 @@
         <v>1396</v>
       </c>
       <c r="E34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="n">
         <v>-0.1190876940824933</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>0.004369268039453192</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>-0.2470334412081985</v>
       </c>
     </row>
@@ -11777,12 +12833,15 @@
         <v>2249</v>
       </c>
       <c r="E35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="2" t="n">
         <v>-0.07819376535294753</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>0.02888191087746534</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>0.4100313479623824</v>
       </c>
     </row>
@@ -11802,12 +12861,15 @@
         <v>2152</v>
       </c>
       <c r="E36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="2" t="n">
         <v>0.01277168049219899</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>0.07093472009059618</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>0.4223397224058162</v>
       </c>
     </row>
@@ -11827,12 +12889,15 @@
         <v>2117</v>
       </c>
       <c r="E37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="2" t="n">
         <v>-0.001587593014590736</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>0.07227480625079405</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>0.2180667433831991</v>
       </c>
     </row>
@@ -11852,12 +12917,15 @@
         <v>1635</v>
       </c>
       <c r="E38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="2" t="n">
         <v>-0.07135102973872924</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>0.01419953746381382</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>-0.2517162471395881</v>
       </c>
     </row>
@@ -11877,12 +12945,15 @@
         <v>2073</v>
       </c>
       <c r="E39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="2" t="n">
         <v>-0.2392134413054473</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>0.228630681202995</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>0.359344262295082</v>
       </c>
     </row>
@@ -11902,12 +12973,15 @@
         <v>2119</v>
       </c>
       <c r="E40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="2" t="n">
         <v>-0.01415033758990166</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>0.08367645803371487</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>-0.06445916114790287</v>
       </c>
     </row>
@@ -11927,12 +13001,15 @@
         <v>2157</v>
       </c>
       <c r="E41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2" t="n">
         <v>0.05725783676927421</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>0.09536981182044227</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>0.7173566878980892</v>
       </c>
     </row>
@@ -11952,12 +13029,15 @@
         <v>1981</v>
       </c>
       <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
         <v>0.08446864990566452</v>
       </c>
-      <c r="F42" s="2" t="n">
+      <c r="G42" s="2" t="n">
         <v>0.09693424971693555</v>
       </c>
-      <c r="G42" s="2" t="n">
+      <c r="H42" s="2" t="n">
         <v>0.6731418918918919</v>
       </c>
     </row>
@@ -11977,12 +13057,15 @@
         <v>1716</v>
       </c>
       <c r="E43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2" t="n">
         <v>0.01022663894944988</v>
       </c>
-      <c r="F43" s="2" t="n">
+      <c r="G43" s="2" t="n">
         <v>0.02860096485182633</v>
       </c>
-      <c r="G43" s="2" t="n">
+      <c r="H43" s="2" t="n">
         <v>0.2257142857142857</v>
       </c>
     </row>
@@ -12002,12 +13085,15 @@
         <v>1453</v>
       </c>
       <c r="E44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="2" t="n">
         <v>-0.0144054379717835</v>
       </c>
-      <c r="F44" s="2" t="n">
+      <c r="G44" s="2" t="n">
         <v>0.01573627554905269</v>
       </c>
-      <c r="G44" s="2" t="n">
+      <c r="H44" s="2" t="n">
         <v>-0.0332667997338656</v>
       </c>
     </row>
@@ -12027,12 +13113,15 @@
         <v>1662</v>
       </c>
       <c r="E45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="2" t="n">
         <v>0.07013026741784995</v>
       </c>
-      <c r="F45" s="2" t="n">
+      <c r="G45" s="2" t="n">
         <v>0.04518265403177511</v>
       </c>
-      <c r="G45" s="2" t="n">
+      <c r="H45" s="2" t="n">
         <v>-0.004790419161676647</v>
       </c>
     </row>
@@ -12052,12 +13141,15 @@
         <v>1540</v>
       </c>
       <c r="E46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="2" t="n">
         <v>0.06887612709317303</v>
       </c>
-      <c r="F46" s="2" t="n">
+      <c r="G46" s="2" t="n">
         <v>0.04197355386139467</v>
       </c>
-      <c r="G46" s="2" t="n">
+      <c r="H46" s="2" t="n">
         <v>0.1031518624641834</v>
       </c>
     </row>
@@ -12077,12 +13169,15 @@
         <v>1667</v>
       </c>
       <c r="E47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="2" t="n">
         <v>0.02042708869402168</v>
       </c>
-      <c r="F47" s="2" t="n">
+      <c r="G47" s="2" t="n">
         <v>-0.006700592560079008</v>
       </c>
-      <c r="G47" s="2" t="n">
+      <c r="H47" s="2" t="n">
         <v>-0.2587816807469986</v>
       </c>
     </row>
@@ -12102,12 +13197,15 @@
         <v>1628</v>
       </c>
       <c r="E48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="2" t="n">
         <v>0.02652937853667238</v>
       </c>
-      <c r="F48" s="2" t="n">
+      <c r="G48" s="2" t="n">
         <v>-0.01536074800164182</v>
       </c>
-      <c r="G48" s="2" t="n">
+      <c r="H48" s="2" t="n">
         <v>-0.2434944237918216</v>
       </c>
     </row>
@@ -12127,12 +13225,15 @@
         <v>1626</v>
       </c>
       <c r="E49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="2" t="n">
         <v>-0.01177984985829565</v>
       </c>
-      <c r="F49" s="2" t="n">
+      <c r="G49" s="2" t="n">
         <v>-0.1026970186169819</v>
       </c>
-      <c r="G49" s="2" t="n">
+      <c r="H49" s="2" t="n">
         <v>-0.2319319792158715</v>
       </c>
     </row>
@@ -12152,12 +13253,15 @@
         <v>1597</v>
       </c>
       <c r="E50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="2" t="n">
         <v>0.1440446015590313</v>
       </c>
-      <c r="F50" s="2" t="n">
+      <c r="G50" s="2" t="n">
         <v>0.03305640158823811</v>
       </c>
-      <c r="G50" s="2" t="n">
+      <c r="H50" s="2" t="n">
         <v>-0.02324159021406728</v>
       </c>
     </row>
@@ -12177,12 +13281,15 @@
         <v>1579</v>
       </c>
       <c r="E51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="2" t="n">
         <v>0.3940591600125655</v>
       </c>
-      <c r="F51" s="2" t="n">
+      <c r="G51" s="2" t="n">
         <v>-0.1718976667254166</v>
       </c>
-      <c r="G51" s="2" t="n">
+      <c r="H51" s="2" t="n">
         <v>-0.2383019778099373</v>
       </c>
     </row>
@@ -12202,12 +13309,15 @@
         <v>1817</v>
       </c>
       <c r="E52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="2" t="n">
         <v>0.05007653619068445</v>
       </c>
-      <c r="F52" s="2" t="n">
+      <c r="G52" s="2" t="n">
         <v>-0.1040910440615929</v>
       </c>
-      <c r="G52" s="2" t="n">
+      <c r="H52" s="2" t="n">
         <v>-0.1425200566304861</v>
       </c>
     </row>
@@ -12227,12 +13337,15 @@
         <v>1543</v>
       </c>
       <c r="E53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="2" t="n">
         <v>0.04655451393347888</v>
       </c>
-      <c r="F53" s="2" t="n">
+      <c r="G53" s="2" t="n">
         <v>-0.1069524103748875</v>
       </c>
-      <c r="G53" s="2" t="n">
+      <c r="H53" s="2" t="n">
         <v>-0.2846546128882708</v>
       </c>
     </row>
@@ -12252,12 +13365,15 @@
         <v>1753</v>
       </c>
       <c r="E54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="2" t="n">
         <v>0.1518644204947175</v>
       </c>
-      <c r="F54" s="2" t="n">
+      <c r="G54" s="2" t="n">
         <v>-0.02435207952558152</v>
       </c>
-      <c r="G54" s="2" t="n">
+      <c r="H54" s="2" t="n">
         <v>-0.1150933871781928</v>
       </c>
     </row>
@@ -12277,12 +13393,15 @@
         <v>1841</v>
       </c>
       <c r="E55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="2" t="n">
         <v>0.1430887290649294</v>
       </c>
-      <c r="F55" s="2" t="n">
+      <c r="G55" s="2" t="n">
         <v>-0.02537524222419286</v>
       </c>
-      <c r="G55" s="2" t="n">
+      <c r="H55" s="2" t="n">
         <v>0.07284382284382285</v>
       </c>
     </row>
@@ -12302,12 +13421,15 @@
         <v>1663</v>
       </c>
       <c r="E56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="2" t="n">
         <v>0.1820364796631634</v>
       </c>
-      <c r="F56" s="2" t="n">
+      <c r="G56" s="2" t="n">
         <v>-0.09698969617685535</v>
       </c>
-      <c r="G56" s="2" t="n">
+      <c r="H56" s="2" t="n">
         <v>0.1445285615966965</v>
       </c>
     </row>
@@ -12327,12 +13449,15 @@
         <v>1585</v>
       </c>
       <c r="E57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="2" t="n">
         <v>0.169817523464672</v>
       </c>
-      <c r="F57" s="2" t="n">
+      <c r="G57" s="2" t="n">
         <v>-0.0770890069296519</v>
       </c>
-      <c r="G57" s="2" t="n">
+      <c r="H57" s="2" t="n">
         <v>-0.04632972322503008</v>
       </c>
     </row>
@@ -12352,12 +13477,15 @@
         <v>1507</v>
       </c>
       <c r="E58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="2" t="n">
         <v>0.1073847745200926</v>
       </c>
-      <c r="F58" s="2" t="n">
+      <c r="G58" s="2" t="n">
         <v>-0.076294015115502</v>
       </c>
-      <c r="G58" s="2" t="n">
+      <c r="H58" s="2" t="n">
         <v>-0.02142857142857143</v>
       </c>
     </row>
@@ -12377,12 +13505,15 @@
         <v>1322</v>
       </c>
       <c r="E59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="2" t="n">
         <v>0.07119959254598837</v>
       </c>
-      <c r="F59" s="2" t="n">
+      <c r="G59" s="2" t="n">
         <v>-0.03372206226567517</v>
       </c>
-      <c r="G59" s="2" t="n">
+      <c r="H59" s="2" t="n">
         <v>-0.2069586082783443</v>
       </c>
     </row>
@@ -12402,12 +13533,15 @@
         <v>1177</v>
       </c>
       <c r="E60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="2" t="n">
         <v>0.03174235403151066</v>
       </c>
-      <c r="F60" s="2" t="n">
+      <c r="G60" s="2" t="n">
         <v>-0.02247500618221641</v>
       </c>
-      <c r="G60" s="2" t="n">
+      <c r="H60" s="2" t="n">
         <v>-0.277027027027027</v>
       </c>
     </row>
@@ -12427,12 +13561,15 @@
         <v>1089</v>
       </c>
       <c r="E61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="2" t="n">
         <v>-0.03020020359687818</v>
       </c>
-      <c r="F61" s="2" t="n">
+      <c r="G61" s="2" t="n">
         <v>-0.009730131220599158</v>
       </c>
-      <c r="G61" s="2" t="n">
+      <c r="H61" s="2" t="n">
         <v>-0.3302583025830259</v>
       </c>
     </row>
@@ -12452,12 +13589,15 @@
         <v>1459</v>
       </c>
       <c r="E62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="2" t="n">
         <v>0.01782266740682154</v>
       </c>
-      <c r="F62" s="2" t="n">
+      <c r="G62" s="2" t="n">
         <v>-0.001281180538404544</v>
       </c>
-      <c r="G62" s="2" t="n">
+      <c r="H62" s="2" t="n">
         <v>-0.08641202254226675</v>
       </c>
     </row>
@@ -12477,12 +13617,15 @@
         <v>1510</v>
       </c>
       <c r="E63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="2" t="n">
         <v>0.07096104767245039</v>
       </c>
-      <c r="F63" s="2" t="n">
+      <c r="G63" s="2" t="n">
         <v>0.1117305173542895</v>
       </c>
-      <c r="G63" s="2" t="n">
+      <c r="H63" s="2" t="n">
         <v>-0.04369854338188727</v>
       </c>
     </row>
@@ -12502,12 +13645,15 @@
         <v>1578</v>
       </c>
       <c r="E64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="2" t="n">
         <v>-0.08815918899040294</v>
       </c>
-      <c r="F64" s="2" t="n">
+      <c r="G64" s="2" t="n">
         <v>-0.0241609285588669</v>
       </c>
-      <c r="G64" s="2" t="n">
+      <c r="H64" s="2" t="n">
         <v>-0.1315354980737479</v>
       </c>
     </row>
@@ -12527,12 +13673,15 @@
         <v>1640</v>
       </c>
       <c r="E65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="2" t="n">
         <v>0.01814585398894659</v>
       </c>
-      <c r="F65" s="2" t="n">
+      <c r="G65" s="2" t="n">
         <v>0.1623863491084656</v>
       </c>
-      <c r="G65" s="2" t="n">
+      <c r="H65" s="2" t="n">
         <v>0.06286454957874271</v>
       </c>
     </row>
@@ -12552,12 +13701,15 @@
         <v>1538</v>
       </c>
       <c r="E66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="2" t="n">
         <v>-0.09266015973164381</v>
       </c>
-      <c r="F66" s="2" t="n">
+      <c r="G66" s="2" t="n">
         <v>0.09725872316338495</v>
       </c>
-      <c r="G66" s="2" t="n">
+      <c r="H66" s="2" t="n">
         <v>-0.1226468910439247</v>
       </c>
     </row>
@@ -12577,12 +13729,15 @@
         <v>1319</v>
       </c>
       <c r="E67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="2" t="n">
         <v>-0.1376379211176824</v>
       </c>
-      <c r="F67" s="2" t="n">
+      <c r="G67" s="2" t="n">
         <v>0.008936996198743698</v>
       </c>
-      <c r="G67" s="2" t="n">
+      <c r="H67" s="2" t="n">
         <v>-0.2835415535035307</v>
       </c>
     </row>
@@ -12602,12 +13757,15 @@
         <v>1405</v>
       </c>
       <c r="E68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="2" t="n">
         <v>-0.1769886877513253</v>
       </c>
-      <c r="F68" s="2" t="n">
+      <c r="G68" s="2" t="n">
         <v>0.2621653956653021</v>
       </c>
-      <c r="G68" s="2" t="n">
+      <c r="H68" s="2" t="n">
         <v>-0.1551413108839447</v>
       </c>
     </row>
@@ -12627,12 +13785,15 @@
         <v>1387</v>
       </c>
       <c r="E69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="2" t="n">
         <v>-0.2374385520479936</v>
       </c>
-      <c r="F69" s="2" t="n">
+      <c r="G69" s="2" t="n">
         <v>0.2075420708192123</v>
       </c>
-      <c r="G69" s="2" t="n">
+      <c r="H69" s="2" t="n">
         <v>-0.1249211356466877</v>
       </c>
     </row>
@@ -12652,12 +13813,15 @@
         <v>1416</v>
       </c>
       <c r="E70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="2" t="n">
         <v>-0.1737833217707526</v>
       </c>
-      <c r="F70" s="2" t="n">
+      <c r="G70" s="2" t="n">
         <v>0.2326981167257132</v>
       </c>
-      <c r="G70" s="2" t="n">
+      <c r="H70" s="2" t="n">
         <v>-0.06038487060384871</v>
       </c>
     </row>
@@ -12677,12 +13841,15 @@
         <v>1490</v>
       </c>
       <c r="E71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2" t="n">
         <v>-0.1308226936469535</v>
       </c>
-      <c r="F71" s="2" t="n">
+      <c r="G71" s="2" t="n">
         <v>0.2660221369518461</v>
       </c>
-      <c r="G71" s="2" t="n">
+      <c r="H71" s="2" t="n">
         <v>0.1270801815431165</v>
       </c>
     </row>
@@ -12702,12 +13869,15 @@
         <v>1327</v>
       </c>
       <c r="E72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2" t="n">
         <v>-0.219201474661277</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="G72" s="2" t="n">
         <v>0.2309944056550588</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="H72" s="2" t="n">
         <v>0.1274426508071368</v>
       </c>
     </row>
@@ -12727,12 +13897,15 @@
         <v>1303</v>
       </c>
       <c r="E73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2" t="n">
         <v>-0.1395121786044832</v>
       </c>
-      <c r="F73" s="2" t="n">
+      <c r="G73" s="2" t="n">
         <v>0.2397429807235543</v>
       </c>
-      <c r="G73" s="2" t="n">
+      <c r="H73" s="2" t="n">
         <v>0.1965105601469238</v>
       </c>
     </row>
@@ -12752,12 +13925,15 @@
         <v>1440</v>
       </c>
       <c r="E74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2" t="n">
         <v>-0.1879009020749171</v>
       </c>
-      <c r="F74" s="2" t="n">
+      <c r="G74" s="2" t="n">
         <v>0.3054512295018624</v>
       </c>
-      <c r="G74" s="2" t="n">
+      <c r="H74" s="2" t="n">
         <v>-0.01302261823166552</v>
       </c>
     </row>
@@ -12777,12 +13953,15 @@
         <v>1491</v>
       </c>
       <c r="E75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2" t="n">
         <v>-0.2473282965688673</v>
       </c>
-      <c r="F75" s="2" t="n">
+      <c r="G75" s="2" t="n">
         <v>0.2375321223188449</v>
       </c>
-      <c r="G75" s="2" t="n">
+      <c r="H75" s="2" t="n">
         <v>-0.01258278145695364</v>
       </c>
     </row>
@@ -12802,12 +13981,15 @@
         <v>1610</v>
       </c>
       <c r="E76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2" t="n">
         <v>-0.1512558492106299</v>
       </c>
-      <c r="F76" s="2" t="n">
+      <c r="G76" s="2" t="n">
         <v>0.3498024537325847</v>
       </c>
-      <c r="G76" s="2" t="n">
+      <c r="H76" s="2" t="n">
         <v>0.02027883396704689</v>
       </c>
     </row>
@@ -12827,12 +14009,15 @@
         <v>1466</v>
       </c>
       <c r="E77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="2" t="n">
         <v>-0.2712705184756671</v>
       </c>
-      <c r="F77" s="2" t="n">
+      <c r="G77" s="2" t="n">
         <v>0.1669125163360635</v>
       </c>
-      <c r="G77" s="2" t="n">
+      <c r="H77" s="2" t="n">
         <v>-0.1060975609756098</v>
       </c>
     </row>
@@ -12852,12 +14037,15 @@
         <v>1273</v>
       </c>
       <c r="E78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="2" t="n">
         <v>-0.2647142794926761</v>
       </c>
-      <c r="F78" s="2" t="n">
+      <c r="G78" s="2" t="n">
         <v>0.1277152384988116</v>
       </c>
-      <c r="G78" s="2" t="n">
+      <c r="H78" s="2" t="n">
         <v>-0.1723016905071521</v>
       </c>
     </row>
@@ -12877,12 +14065,15 @@
         <v>1309</v>
       </c>
       <c r="E79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="2" t="n">
         <v>-0.247488658870011</v>
       </c>
-      <c r="F79" s="2" t="n">
+      <c r="G79" s="2" t="n">
         <v>0.2066961482451335</v>
       </c>
-      <c r="G79" s="2" t="n">
+      <c r="H79" s="2" t="n">
         <v>-0.007581501137225171</v>
       </c>
     </row>
@@ -12902,12 +14093,15 @@
         <v>1419</v>
       </c>
       <c r="E80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="2" t="n">
         <v>-0.1407687929353554</v>
       </c>
-      <c r="F80" s="2" t="n">
+      <c r="G80" s="2" t="n">
         <v>0.1575692702523198</v>
       </c>
-      <c r="G80" s="2" t="n">
+      <c r="H80" s="2" t="n">
         <v>0.0099644128113879</v>
       </c>
     </row>
@@ -12927,12 +14121,15 @@
         <v>1310</v>
       </c>
       <c r="E81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="2" t="n">
         <v>-0.2090859566104447</v>
       </c>
-      <c r="F81" s="2" t="n">
+      <c r="G81" s="2" t="n">
         <v>0.09297331954248247</v>
       </c>
-      <c r="G81" s="2" t="n">
+      <c r="H81" s="2" t="n">
         <v>-0.0555155010814708</v>
       </c>
     </row>
@@ -12952,12 +14149,15 @@
         <v>1512</v>
       </c>
       <c r="E82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="2" t="n">
         <v>-0.1277845159236717</v>
       </c>
-      <c r="F82" s="2" t="n">
+      <c r="G82" s="2" t="n">
         <v>0.123455594951414</v>
       </c>
-      <c r="G82" s="2" t="n">
+      <c r="H82" s="2" t="n">
         <v>0.06779661016949153</v>
       </c>
     </row>
@@ -12977,12 +14177,15 @@
         <v>1676</v>
       </c>
       <c r="E83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="2" t="n">
         <v>-0.1038334888610012</v>
       </c>
-      <c r="F83" s="2" t="n">
+      <c r="G83" s="2" t="n">
         <v>0.05803269065787691</v>
       </c>
-      <c r="G83" s="2" t="n">
+      <c r="H83" s="2" t="n">
         <v>0.1248322147651007</v>
       </c>
     </row>
@@ -13002,12 +14205,15 @@
         <v>1305</v>
       </c>
       <c r="E84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="2" t="n">
         <v>-0.1364962760124872</v>
       </c>
-      <c r="F84" s="2" t="n">
+      <c r="G84" s="2" t="n">
         <v>-0.008155572387310423</v>
       </c>
-      <c r="G84" s="2" t="n">
+      <c r="H84" s="2" t="n">
         <v>-0.01657874905802562</v>
       </c>
     </row>
@@ -13027,12 +14233,15 @@
         <v>1189</v>
       </c>
       <c r="E85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="2" t="n">
         <v>-0.07873421872438105</v>
       </c>
-      <c r="F85" s="2" t="n">
+      <c r="G85" s="2" t="n">
         <v>0.03658290646553463</v>
       </c>
-      <c r="G85" s="2" t="n">
+      <c r="H85" s="2" t="n">
         <v>-0.08749040675364543</v>
       </c>
     </row>
@@ -13052,12 +14261,15 @@
         <v>1126</v>
       </c>
       <c r="E86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="2" t="n">
         <v>-0.1801162500445744</v>
       </c>
-      <c r="F86" s="2" t="n">
+      <c r="G86" s="2" t="n">
         <v>-0.1342228641788218</v>
       </c>
-      <c r="G86" s="2" t="n">
+      <c r="H86" s="2" t="n">
         <v>-0.2180555555555556</v>
       </c>
     </row>
@@ -13077,12 +14289,15 @@
         <v>1299</v>
       </c>
       <c r="E87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="2" t="n">
         <v>-0.03106898367561875</v>
       </c>
-      <c r="F87" s="2" t="n">
+      <c r="G87" s="2" t="n">
         <v>-0.08753004736178213</v>
       </c>
-      <c r="G87" s="2" t="n">
+      <c r="H87" s="2" t="n">
         <v>-0.1287726358148893</v>
       </c>
     </row>
@@ -13102,12 +14317,15 @@
         <v>1583</v>
       </c>
       <c r="E88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="2" t="n">
         <v>-0.01212006709834029</v>
       </c>
-      <c r="F88" s="2" t="n">
+      <c r="G88" s="2" t="n">
         <v>-0.07195382466518774</v>
       </c>
-      <c r="G88" s="2" t="n">
+      <c r="H88" s="2" t="n">
         <v>-0.01677018633540373</v>
       </c>
     </row>
@@ -13127,12 +14345,15 @@
         <v>1190</v>
       </c>
       <c r="E89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="2" t="n">
         <v>0.1294488105633617</v>
       </c>
-      <c r="F89" s="2" t="n">
+      <c r="G89" s="2" t="n">
         <v>-0.04745377429102098</v>
       </c>
-      <c r="G89" s="2" t="n">
+      <c r="H89" s="2" t="n">
         <v>-0.1882673942701228</v>
       </c>
     </row>
@@ -13152,12 +14373,15 @@
         <v>1189</v>
       </c>
       <c r="E90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="2" t="n">
         <v>0.2368492059835866</v>
       </c>
-      <c r="F90" s="2" t="n">
+      <c r="G90" s="2" t="n">
         <v>-0.1624924439216455</v>
       </c>
-      <c r="G90" s="2" t="n">
+      <c r="H90" s="2" t="n">
         <v>-0.06598586017282011</v>
       </c>
     </row>
@@ -13177,12 +14401,15 @@
         <v>1402</v>
       </c>
       <c r="E91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="2" t="n">
         <v>0.3565629228687415</v>
       </c>
-      <c r="F91" s="2" t="n">
+      <c r="G91" s="2" t="n">
         <v>-0.1711138175376439</v>
       </c>
-      <c r="G91" s="2" t="n">
+      <c r="H91" s="2" t="n">
         <v>0.07104660045836517</v>
       </c>
     </row>
@@ -13202,12 +14429,15 @@
         <v>1134</v>
       </c>
       <c r="E92" s="2" t="n">
+        <v>8202</v>
+      </c>
+      <c r="F92" s="2" t="n">
         <v>0.2038132591756959</v>
       </c>
-      <c r="F92" s="2" t="n">
+      <c r="G92" s="2" t="n">
         <v>-0.2051783396558543</v>
       </c>
-      <c r="G92" s="2" t="n">
+      <c r="H92" s="2" t="n">
         <v>-0.200845665961945</v>
       </c>
     </row>
@@ -13222,7 +14452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -13252,7 +14482,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Coverage: Ambassador Bridge, Blue Water Bridge, Detroit-Windsor Tunnel -- bidirectional (both directions combined), operator-reported.</t>
+          <t>Coverage: Ambassador Bridge, Blue Water Bridge, Detroit-Windsor Tunnel, Gordie Howe International Bridge -- bidirectional (both directions combined), operator-reported. GHIB opened July 27, 2026, so its columns are blank before then and partial for its first (July 2026) month.</t>
         </is>
       </c>
     </row>
@@ -13273,21 +14503,28 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Date range shown: 2019-present. Underlying source data goes back further (to 2006) and is used internally to compute YoY % for 2019, but only 2019+ rows are shown.</t>
+          <t>Monthly snapshot tabs: One tab per month from August 2026 onward (e.g. 'August 2026'), formatted for a bar chart: crossing, this month vs. same month prior year, pct_change, category (Total/Cars/Trucks). A new tab appears automatically once that month is reported.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>YoY %: (this month - same month prior year) / prior year.</t>
+          <t>Date range shown: 2019-present. Underlying source data goes back further (to 2006) and is used internally to compute YoY % for 2019, but only 2019+ rows are shown.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 19:59 UTC</t>
+          <t>YoY %: (this month - same month prior year) / prior year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Rebuilt: 2026-09-11 20:09 UTC</t>
         </is>
       </c>
     </row>

--- a/data/btoa_traffic_analysis.xlsx
+++ b/data/btoa_traffic_analysis.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/btoa_traffic_analysis.xlsx
+++ b/data/btoa_traffic_analysis.xlsx
@@ -1,17 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall traffic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Car traffic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Truck traffic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August 2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -436,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F274"/>
+  <dimension ref="A1:F277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -515,9 +516,6 @@
       <c r="D3" t="n">
         <v>305531</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -539,9 +537,6 @@
       <c r="D4" t="n">
         <v>818</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -584,9 +579,6 @@
       <c r="D6" t="n">
         <v>301919</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -608,9 +600,6 @@
       <c r="D7" t="n">
         <v>834</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -653,9 +642,6 @@
       <c r="D9" t="n">
         <v>352582</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -677,9 +663,6 @@
       <c r="D10" t="n">
         <v>895</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -722,9 +705,6 @@
       <c r="D12" t="n">
         <v>347738</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -746,9 +726,6 @@
       <c r="D13" t="n">
         <v>980</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -791,9 +768,6 @@
       <c r="D15" t="n">
         <v>363015</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -815,9 +789,6 @@
       <c r="D16" t="n">
         <v>1057</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -860,9 +831,6 @@
       <c r="D18" t="n">
         <v>353264</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -884,9 +852,6 @@
       <c r="D19" t="n">
         <v>969</v>
       </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -929,9 +894,6 @@
       <c r="D21" t="n">
         <v>352049</v>
       </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -953,9 +915,6 @@
       <c r="D22" t="n">
         <v>964</v>
       </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -998,9 +957,6 @@
       <c r="D24" t="n">
         <v>386184</v>
       </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1022,9 +978,6 @@
       <c r="D25" t="n">
         <v>1009</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1067,9 +1020,6 @@
       <c r="D27" t="n">
         <v>355165</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1091,9 +1041,6 @@
       <c r="D28" t="n">
         <v>928</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1136,9 +1083,6 @@
       <c r="D30" t="n">
         <v>363343</v>
       </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1160,9 +1104,6 @@
       <c r="D31" t="n">
         <v>1019</v>
       </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1205,9 +1146,6 @@
       <c r="D33" t="n">
         <v>341197</v>
       </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1229,9 +1167,6 @@
       <c r="D34" t="n">
         <v>916</v>
       </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1274,9 +1209,6 @@
       <c r="D36" t="n">
         <v>355306</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1298,9 +1230,6 @@
       <c r="D37" t="n">
         <v>757</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1343,9 +1272,6 @@
       <c r="D39" t="n">
         <v>331282</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1367,9 +1293,6 @@
       <c r="D40" t="n">
         <v>833</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1412,9 +1335,6 @@
       <c r="D42" t="n">
         <v>320647</v>
       </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1436,9 +1356,6 @@
       <c r="D43" t="n">
         <v>806</v>
       </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1481,9 +1398,6 @@
       <c r="D45" t="n">
         <v>189636</v>
       </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1505,9 +1419,6 @@
       <c r="D46" t="n">
         <v>823</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1550,9 +1461,6 @@
       <c r="D48" t="n">
         <v>36729</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1574,9 +1482,6 @@
       <c r="D49" t="n">
         <v>441</v>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1619,9 +1524,6 @@
       <c r="D51" t="n">
         <v>41426</v>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1643,9 +1545,6 @@
       <c r="D52" t="n">
         <v>510</v>
       </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1688,9 +1587,6 @@
       <c r="D54" t="n">
         <v>53232</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1712,9 +1608,6 @@
       <c r="D55" t="n">
         <v>573</v>
       </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1757,9 +1650,6 @@
       <c r="D57" t="n">
         <v>60372</v>
       </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1781,9 +1671,6 @@
       <c r="D58" t="n">
         <v>684</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1826,9 +1713,6 @@
       <c r="D60" t="n">
         <v>62737</v>
       </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1850,9 +1734,6 @@
       <c r="D61" t="n">
         <v>894</v>
       </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1895,9 +1776,6 @@
       <c r="D63" t="n">
         <v>67048</v>
       </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1919,9 +1797,6 @@
       <c r="D64" t="n">
         <v>1854</v>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -1964,9 +1839,6 @@
       <c r="D66" t="n">
         <v>68944</v>
       </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -1988,9 +1860,6 @@
       <c r="D67" t="n">
         <v>1595</v>
       </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2033,9 +1902,6 @@
       <c r="D69" t="n">
         <v>61408</v>
       </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2057,9 +1923,6 @@
       <c r="D70" t="n">
         <v>1513</v>
       </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2102,9 +1965,6 @@
       <c r="D72" t="n">
         <v>60990</v>
       </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
       <c r="F72" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2126,9 +1986,6 @@
       <c r="D73" t="n">
         <v>1738</v>
       </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2171,9 +2028,6 @@
       <c r="D75" t="n">
         <v>60140</v>
       </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
       <c r="F75" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2195,9 +2049,6 @@
       <c r="D76" t="n">
         <v>2185</v>
       </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2240,9 +2091,6 @@
       <c r="D78" t="n">
         <v>58779</v>
       </c>
-      <c r="E78" t="n">
-        <v>0</v>
-      </c>
       <c r="F78" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2264,9 +2112,6 @@
       <c r="D79" t="n">
         <v>1525</v>
       </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
       <c r="F79" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2309,9 +2154,6 @@
       <c r="D81" t="n">
         <v>74139</v>
       </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
       <c r="F81" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2333,9 +2175,6 @@
       <c r="D82" t="n">
         <v>2265</v>
       </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
       <c r="F82" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2378,9 +2217,6 @@
       <c r="D84" t="n">
         <v>69787</v>
       </c>
-      <c r="E84" t="n">
-        <v>0</v>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2402,9 +2238,6 @@
       <c r="D85" t="n">
         <v>1256</v>
       </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
       <c r="F85" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2447,9 +2280,6 @@
       <c r="D87" t="n">
         <v>70760</v>
       </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2471,9 +2301,6 @@
       <c r="D88" t="n">
         <v>1184</v>
       </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
       <c r="F88" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2516,9 +2343,6 @@
       <c r="D90" t="n">
         <v>77793</v>
       </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
       <c r="F90" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2540,9 +2364,6 @@
       <c r="D91" t="n">
         <v>1400</v>
       </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2585,9 +2406,6 @@
       <c r="D93" t="n">
         <v>77550</v>
       </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
       <c r="F93" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2609,9 +2427,6 @@
       <c r="D94" t="n">
         <v>1503</v>
       </c>
-      <c r="E94" t="n">
-        <v>0</v>
-      </c>
       <c r="F94" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2654,9 +2469,6 @@
       <c r="D96" t="n">
         <v>95360</v>
       </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
       <c r="F96" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2678,9 +2490,6 @@
       <c r="D97" t="n">
         <v>1670</v>
       </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2723,9 +2532,6 @@
       <c r="D99" t="n">
         <v>99306</v>
       </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2747,9 +2553,6 @@
       <c r="D100" t="n">
         <v>1396</v>
       </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
       <c r="F100" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2792,9 +2595,6 @@
       <c r="D102" t="n">
         <v>107093</v>
       </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
       <c r="F102" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2816,9 +2616,6 @@
       <c r="D103" t="n">
         <v>2249</v>
       </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
       <c r="F103" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2861,9 +2658,6 @@
       <c r="D105" t="n">
         <v>116854</v>
       </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
       <c r="F105" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2885,9 +2679,6 @@
       <c r="D106" t="n">
         <v>2152</v>
       </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
       <c r="F106" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2930,9 +2721,6 @@
       <c r="D108" t="n">
         <v>138709</v>
       </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
       <c r="F108" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -2954,9 +2742,6 @@
       <c r="D109" t="n">
         <v>2117</v>
       </c>
-      <c r="E109" t="n">
-        <v>0</v>
-      </c>
       <c r="F109" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -2999,9 +2784,6 @@
       <c r="D111" t="n">
         <v>122008</v>
       </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
       <c r="F111" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3023,9 +2805,6 @@
       <c r="D112" t="n">
         <v>1635</v>
       </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
       <c r="F112" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3068,9 +2847,6 @@
       <c r="D114" t="n">
         <v>254203</v>
       </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
       <c r="F114" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3092,9 +2868,6 @@
       <c r="D115" t="n">
         <v>2073</v>
       </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3137,9 +2910,6 @@
       <c r="D117" t="n">
         <v>186188</v>
       </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
       <c r="F117" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3161,9 +2931,6 @@
       <c r="D118" t="n">
         <v>2119</v>
       </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
       <c r="F118" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3206,9 +2973,6 @@
       <c r="D120" t="n">
         <v>231095</v>
       </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
       <c r="F120" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3230,9 +2994,6 @@
       <c r="D121" t="n">
         <v>2157</v>
       </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
       <c r="F121" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3275,9 +3036,6 @@
       <c r="D123" t="n">
         <v>251098</v>
       </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
       <c r="F123" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3299,9 +3057,6 @@
       <c r="D124" t="n">
         <v>1981</v>
       </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
       <c r="F124" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3344,9 +3099,6 @@
       <c r="D126" t="n">
         <v>253099</v>
       </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
       <c r="F126" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3368,9 +3120,6 @@
       <c r="D127" t="n">
         <v>1716</v>
       </c>
-      <c r="E127" t="n">
-        <v>0</v>
-      </c>
       <c r="F127" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3413,9 +3162,6 @@
       <c r="D129" t="n">
         <v>258656</v>
       </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3437,9 +3183,6 @@
       <c r="D130" t="n">
         <v>1453</v>
       </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3482,9 +3225,6 @@
       <c r="D132" t="n">
         <v>271077</v>
       </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
       <c r="F132" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3506,9 +3246,6 @@
       <c r="D133" t="n">
         <v>1662</v>
       </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
       <c r="F133" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3551,9 +3288,6 @@
       <c r="D135" t="n">
         <v>265158</v>
       </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
       <c r="F135" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3575,9 +3309,6 @@
       <c r="D136" t="n">
         <v>1540</v>
       </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
       <c r="F136" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3620,9 +3351,6 @@
       <c r="D138" t="n">
         <v>299790</v>
       </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
       <c r="F138" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3644,9 +3372,6 @@
       <c r="D139" t="n">
         <v>1667</v>
       </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
       <c r="F139" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3689,9 +3414,6 @@
       <c r="D141" t="n">
         <v>280295</v>
       </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
       <c r="F141" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3713,9 +3435,6 @@
       <c r="D142" t="n">
         <v>1628</v>
       </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
       <c r="F142" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3758,9 +3477,6 @@
       <c r="D144" t="n">
         <v>274780</v>
       </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
       <c r="F144" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3782,9 +3498,6 @@
       <c r="D145" t="n">
         <v>1626</v>
       </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3827,9 +3540,6 @@
       <c r="D147" t="n">
         <v>271687</v>
       </c>
-      <c r="E147" t="n">
-        <v>0</v>
-      </c>
       <c r="F147" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3851,9 +3561,6 @@
       <c r="D148" t="n">
         <v>1597</v>
       </c>
-      <c r="E148" t="n">
-        <v>0</v>
-      </c>
       <c r="F148" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3896,9 +3603,6 @@
       <c r="D150" t="n">
         <v>260576</v>
       </c>
-      <c r="E150" t="n">
-        <v>0</v>
-      </c>
       <c r="F150" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3920,9 +3624,6 @@
       <c r="D151" t="n">
         <v>1579</v>
       </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
       <c r="F151" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -3965,9 +3666,6 @@
       <c r="D153" t="n">
         <v>297718</v>
       </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
       <c r="F153" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -3989,9 +3687,6 @@
       <c r="D154" t="n">
         <v>1817</v>
       </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
       <c r="F154" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4034,9 +3729,6 @@
       <c r="D156" t="n">
         <v>276772</v>
       </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
       <c r="F156" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4058,9 +3750,6 @@
       <c r="D157" t="n">
         <v>1543</v>
       </c>
-      <c r="E157" t="n">
-        <v>0</v>
-      </c>
       <c r="F157" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4103,9 +3792,6 @@
       <c r="D159" t="n">
         <v>304408</v>
       </c>
-      <c r="E159" t="n">
-        <v>0</v>
-      </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4127,9 +3813,6 @@
       <c r="D160" t="n">
         <v>1753</v>
       </c>
-      <c r="E160" t="n">
-        <v>0</v>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4172,9 +3855,6 @@
       <c r="D162" t="n">
         <v>287581</v>
       </c>
-      <c r="E162" t="n">
-        <v>0</v>
-      </c>
       <c r="F162" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4196,9 +3876,6 @@
       <c r="D163" t="n">
         <v>1841</v>
       </c>
-      <c r="E163" t="n">
-        <v>0</v>
-      </c>
       <c r="F163" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4241,9 +3918,6 @@
       <c r="D165" t="n">
         <v>328074</v>
       </c>
-      <c r="E165" t="n">
-        <v>0</v>
-      </c>
       <c r="F165" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4265,9 +3939,6 @@
       <c r="D166" t="n">
         <v>1663</v>
       </c>
-      <c r="E166" t="n">
-        <v>0</v>
-      </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4310,9 +3981,6 @@
       <c r="D168" t="n">
         <v>354853</v>
       </c>
-      <c r="E168" t="n">
-        <v>0</v>
-      </c>
       <c r="F168" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4334,9 +4002,6 @@
       <c r="D169" t="n">
         <v>1585</v>
       </c>
-      <c r="E169" t="n">
-        <v>0</v>
-      </c>
       <c r="F169" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4379,9 +4044,6 @@
       <c r="D171" t="n">
         <v>325925</v>
       </c>
-      <c r="E171" t="n">
-        <v>0</v>
-      </c>
       <c r="F171" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4403,9 +4065,6 @@
       <c r="D172" t="n">
         <v>1507</v>
       </c>
-      <c r="E172" t="n">
-        <v>0</v>
-      </c>
       <c r="F172" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4448,9 +4107,6 @@
       <c r="D174" t="n">
         <v>335998</v>
       </c>
-      <c r="E174" t="n">
-        <v>0</v>
-      </c>
       <c r="F174" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4472,9 +4128,6 @@
       <c r="D175" t="n">
         <v>1322</v>
       </c>
-      <c r="E175" t="n">
-        <v>0</v>
-      </c>
       <c r="F175" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4517,9 +4170,6 @@
       <c r="D177" t="n">
         <v>324531</v>
       </c>
-      <c r="E177" t="n">
-        <v>0</v>
-      </c>
       <c r="F177" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4541,9 +4191,6 @@
       <c r="D178" t="n">
         <v>1177</v>
       </c>
-      <c r="E178" t="n">
-        <v>0</v>
-      </c>
       <c r="F178" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4586,9 +4233,6 @@
       <c r="D180" t="n">
         <v>312232</v>
       </c>
-      <c r="E180" t="n">
-        <v>0</v>
-      </c>
       <c r="F180" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4610,9 +4254,6 @@
       <c r="D181" t="n">
         <v>1089</v>
       </c>
-      <c r="E181" t="n">
-        <v>0</v>
-      </c>
       <c r="F181" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4655,9 +4296,6 @@
       <c r="D183" t="n">
         <v>291915</v>
       </c>
-      <c r="E183" t="n">
-        <v>0</v>
-      </c>
       <c r="F183" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4679,9 +4317,6 @@
       <c r="D184" t="n">
         <v>1459</v>
       </c>
-      <c r="E184" t="n">
-        <v>0</v>
-      </c>
       <c r="F184" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4724,9 +4359,6 @@
       <c r="D186" t="n">
         <v>300009</v>
       </c>
-      <c r="E186" t="n">
-        <v>0</v>
-      </c>
       <c r="F186" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4748,9 +4380,6 @@
       <c r="D187" t="n">
         <v>1510</v>
       </c>
-      <c r="E187" t="n">
-        <v>0</v>
-      </c>
       <c r="F187" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4793,9 +4422,6 @@
       <c r="D189" t="n">
         <v>323430</v>
       </c>
-      <c r="E189" t="n">
-        <v>0</v>
-      </c>
       <c r="F189" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4817,9 +4443,6 @@
       <c r="D190" t="n">
         <v>1578</v>
       </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
       <c r="F190" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4862,9 +4485,6 @@
       <c r="D192" t="n">
         <v>292727</v>
       </c>
-      <c r="E192" t="n">
-        <v>0</v>
-      </c>
       <c r="F192" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4886,9 +4506,6 @@
       <c r="D193" t="n">
         <v>1640</v>
       </c>
-      <c r="E193" t="n">
-        <v>0</v>
-      </c>
       <c r="F193" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -4931,9 +4548,6 @@
       <c r="D195" t="n">
         <v>315508</v>
       </c>
-      <c r="E195" t="n">
-        <v>0</v>
-      </c>
       <c r="F195" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -4955,9 +4569,6 @@
       <c r="D196" t="n">
         <v>1538</v>
       </c>
-      <c r="E196" t="n">
-        <v>0</v>
-      </c>
       <c r="F196" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5000,9 +4611,6 @@
       <c r="D198" t="n">
         <v>307762</v>
       </c>
-      <c r="E198" t="n">
-        <v>0</v>
-      </c>
       <c r="F198" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5024,9 +4632,6 @@
       <c r="D199" t="n">
         <v>1319</v>
       </c>
-      <c r="E199" t="n">
-        <v>0</v>
-      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5069,9 +4674,6 @@
       <c r="D201" t="n">
         <v>338006</v>
       </c>
-      <c r="E201" t="n">
-        <v>0</v>
-      </c>
       <c r="F201" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5093,9 +4695,6 @@
       <c r="D202" t="n">
         <v>1405</v>
       </c>
-      <c r="E202" t="n">
-        <v>0</v>
-      </c>
       <c r="F202" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5138,9 +4737,6 @@
       <c r="D204" t="n">
         <v>353703</v>
       </c>
-      <c r="E204" t="n">
-        <v>0</v>
-      </c>
       <c r="F204" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5162,9 +4758,6 @@
       <c r="D205" t="n">
         <v>1387</v>
       </c>
-      <c r="E205" t="n">
-        <v>0</v>
-      </c>
       <c r="F205" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5207,9 +4800,6 @@
       <c r="D207" t="n">
         <v>330318</v>
       </c>
-      <c r="E207" t="n">
-        <v>0</v>
-      </c>
       <c r="F207" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5231,9 +4821,6 @@
       <c r="D208" t="n">
         <v>1416</v>
       </c>
-      <c r="E208" t="n">
-        <v>0</v>
-      </c>
       <c r="F208" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5276,9 +4863,6 @@
       <c r="D210" t="n">
         <v>346933</v>
       </c>
-      <c r="E210" t="n">
-        <v>0</v>
-      </c>
       <c r="F210" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5300,9 +4884,6 @@
       <c r="D211" t="n">
         <v>1490</v>
       </c>
-      <c r="E211" t="n">
-        <v>0</v>
-      </c>
       <c r="F211" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5345,9 +4926,6 @@
       <c r="D213" t="n">
         <v>317027</v>
       </c>
-      <c r="E213" t="n">
-        <v>0</v>
-      </c>
       <c r="F213" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5369,9 +4947,6 @@
       <c r="D214" t="n">
         <v>1327</v>
       </c>
-      <c r="E214" t="n">
-        <v>0</v>
-      </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5414,9 +4989,6 @@
       <c r="D216" t="n">
         <v>318346</v>
       </c>
-      <c r="E216" t="n">
-        <v>0</v>
-      </c>
       <c r="F216" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5438,9 +5010,6 @@
       <c r="D217" t="n">
         <v>1303</v>
       </c>
-      <c r="E217" t="n">
-        <v>0</v>
-      </c>
       <c r="F217" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5483,9 +5052,6 @@
       <c r="D219" t="n">
         <v>304619</v>
       </c>
-      <c r="E219" t="n">
-        <v>0</v>
-      </c>
       <c r="F219" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5507,9 +5073,6 @@
       <c r="D220" t="n">
         <v>1440</v>
       </c>
-      <c r="E220" t="n">
-        <v>0</v>
-      </c>
       <c r="F220" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5552,9 +5115,6 @@
       <c r="D222" t="n">
         <v>273738</v>
       </c>
-      <c r="E222" t="n">
-        <v>0</v>
-      </c>
       <c r="F222" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5576,9 +5136,6 @@
       <c r="D223" t="n">
         <v>1491</v>
       </c>
-      <c r="E223" t="n">
-        <v>0</v>
-      </c>
       <c r="F223" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5621,9 +5178,6 @@
       <c r="D225" t="n">
         <v>317779</v>
       </c>
-      <c r="E225" t="n">
-        <v>0</v>
-      </c>
       <c r="F225" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5645,9 +5199,6 @@
       <c r="D226" t="n">
         <v>1610</v>
       </c>
-      <c r="E226" t="n">
-        <v>0</v>
-      </c>
       <c r="F226" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5690,9 +5241,6 @@
       <c r="D228" t="n">
         <v>303248</v>
       </c>
-      <c r="E228" t="n">
-        <v>0</v>
-      </c>
       <c r="F228" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5714,9 +5262,6 @@
       <c r="D229" t="n">
         <v>1466</v>
       </c>
-      <c r="E229" t="n">
-        <v>0</v>
-      </c>
       <c r="F229" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5759,9 +5304,6 @@
       <c r="D231" t="n">
         <v>299344</v>
       </c>
-      <c r="E231" t="n">
-        <v>0</v>
-      </c>
       <c r="F231" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5783,9 +5325,6 @@
       <c r="D232" t="n">
         <v>1273</v>
       </c>
-      <c r="E232" t="n">
-        <v>0</v>
-      </c>
       <c r="F232" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5828,9 +5367,6 @@
       <c r="D234" t="n">
         <v>304231</v>
       </c>
-      <c r="E234" t="n">
-        <v>0</v>
-      </c>
       <c r="F234" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5852,9 +5388,6 @@
       <c r="D235" t="n">
         <v>1309</v>
       </c>
-      <c r="E235" t="n">
-        <v>0</v>
-      </c>
       <c r="F235" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5897,9 +5430,6 @@
       <c r="D237" t="n">
         <v>331296</v>
       </c>
-      <c r="E237" t="n">
-        <v>0</v>
-      </c>
       <c r="F237" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5921,9 +5451,6 @@
       <c r="D238" t="n">
         <v>1419</v>
       </c>
-      <c r="E238" t="n">
-        <v>0</v>
-      </c>
       <c r="F238" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -5966,9 +5493,6 @@
       <c r="D240" t="n">
         <v>340375</v>
       </c>
-      <c r="E240" t="n">
-        <v>0</v>
-      </c>
       <c r="F240" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -5990,9 +5514,6 @@
       <c r="D241" t="n">
         <v>1310</v>
       </c>
-      <c r="E241" t="n">
-        <v>0</v>
-      </c>
       <c r="F241" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6035,9 +5556,6 @@
       <c r="D243" t="n">
         <v>323331</v>
       </c>
-      <c r="E243" t="n">
-        <v>0</v>
-      </c>
       <c r="F243" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6059,9 +5577,6 @@
       <c r="D244" t="n">
         <v>1512</v>
       </c>
-      <c r="E244" t="n">
-        <v>0</v>
-      </c>
       <c r="F244" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6104,9 +5619,6 @@
       <c r="D246" t="n">
         <v>341108</v>
       </c>
-      <c r="E246" t="n">
-        <v>0</v>
-      </c>
       <c r="F246" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6128,9 +5640,6 @@
       <c r="D247" t="n">
         <v>1676</v>
       </c>
-      <c r="E247" t="n">
-        <v>0</v>
-      </c>
       <c r="F247" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6173,9 +5682,6 @@
       <c r="D249" t="n">
         <v>302866</v>
       </c>
-      <c r="E249" t="n">
-        <v>0</v>
-      </c>
       <c r="F249" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6197,9 +5703,6 @@
       <c r="D250" t="n">
         <v>1305</v>
       </c>
-      <c r="E250" t="n">
-        <v>0</v>
-      </c>
       <c r="F250" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6242,9 +5745,6 @@
       <c r="D252" t="n">
         <v>300939</v>
       </c>
-      <c r="E252" t="n">
-        <v>0</v>
-      </c>
       <c r="F252" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6266,9 +5766,6 @@
       <c r="D253" t="n">
         <v>1189</v>
       </c>
-      <c r="E253" t="n">
-        <v>0</v>
-      </c>
       <c r="F253" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6311,9 +5808,6 @@
       <c r="D255" t="n">
         <v>289016</v>
       </c>
-      <c r="E255" t="n">
-        <v>0</v>
-      </c>
       <c r="F255" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6335,9 +5829,6 @@
       <c r="D256" t="n">
         <v>1126</v>
       </c>
-      <c r="E256" t="n">
-        <v>0</v>
-      </c>
       <c r="F256" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6380,9 +5871,6 @@
       <c r="D258" t="n">
         <v>291368</v>
       </c>
-      <c r="E258" t="n">
-        <v>0</v>
-      </c>
       <c r="F258" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6404,9 +5892,6 @@
       <c r="D259" t="n">
         <v>1299</v>
       </c>
-      <c r="E259" t="n">
-        <v>0</v>
-      </c>
       <c r="F259" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6449,9 +5934,6 @@
       <c r="D261" t="n">
         <v>329281</v>
       </c>
-      <c r="E261" t="n">
-        <v>0</v>
-      </c>
       <c r="F261" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6473,9 +5955,6 @@
       <c r="D262" t="n">
         <v>1583</v>
       </c>
-      <c r="E262" t="n">
-        <v>0</v>
-      </c>
       <c r="F262" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6518,9 +5997,6 @@
       <c r="D264" t="n">
         <v>322513</v>
       </c>
-      <c r="E264" t="n">
-        <v>0</v>
-      </c>
       <c r="F264" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6542,9 +6018,6 @@
       <c r="D265" t="n">
         <v>1190</v>
       </c>
-      <c r="E265" t="n">
-        <v>0</v>
-      </c>
       <c r="F265" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6587,9 +6060,6 @@
       <c r="D267" t="n">
         <v>304982</v>
       </c>
-      <c r="E267" t="n">
-        <v>0</v>
-      </c>
       <c r="F267" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6611,9 +6081,6 @@
       <c r="D268" t="n">
         <v>1189</v>
       </c>
-      <c r="E268" t="n">
-        <v>0</v>
-      </c>
       <c r="F268" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6656,9 +6123,6 @@
       <c r="D270" t="n">
         <v>320046</v>
       </c>
-      <c r="E270" t="n">
-        <v>0</v>
-      </c>
       <c r="F270" t="inlineStr">
         <is>
           <t>Passenger cars</t>
@@ -6680,9 +6144,6 @@
       <c r="D271" t="n">
         <v>1402</v>
       </c>
-      <c r="E271" t="n">
-        <v>0</v>
-      </c>
       <c r="F271" t="inlineStr">
         <is>
           <t>Trucks</t>
@@ -6756,6 +6217,78 @@
         <v>8202</v>
       </c>
       <c r="F274" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>345445</v>
+      </c>
+      <c r="C275" t="n">
+        <v>333986</v>
+      </c>
+      <c r="D275" t="n">
+        <v>282880</v>
+      </c>
+      <c r="E275" t="n">
+        <v>343507</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Total vehicles</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>195796</v>
+      </c>
+      <c r="C276" t="n">
+        <v>202160</v>
+      </c>
+      <c r="D276" t="n">
+        <v>280955</v>
+      </c>
+      <c r="E276" t="n">
+        <v>269716</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Passenger cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>149649</v>
+      </c>
+      <c r="C277" t="n">
+        <v>131581</v>
+      </c>
+      <c r="D277" t="n">
+        <v>952</v>
+      </c>
+      <c r="E277" t="n">
+        <v>73791</v>
+      </c>
+      <c r="F277" t="inlineStr">
         <is>
           <t>Trucks</t>
         </is>
@@ -6772,7 +6305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9201,6 +8734,34 @@
         <v>-0.02172117163227556</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>345445</v>
+      </c>
+      <c r="C93" t="n">
+        <v>333986</v>
+      </c>
+      <c r="D93" t="n">
+        <v>282880</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>343507</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-0.2992206011230484</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>-0.104263775874184</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>-0.1755509830551945</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9212,7 +8773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9288,9 +8849,7 @@
       <c r="D2" t="n">
         <v>305531</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n">
         <v>-0.080884266719829</v>
       </c>
@@ -9316,9 +8875,7 @@
       <c r="D3" t="n">
         <v>301919</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n">
         <v>-0.030971935944189</v>
       </c>
@@ -9344,9 +8901,7 @@
       <c r="D4" t="n">
         <v>352582</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n">
         <v>-0.02822559823189813</v>
       </c>
@@ -9372,9 +8927,7 @@
       <c r="D5" t="n">
         <v>347738</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n">
         <v>-0.04002598467543117</v>
       </c>
@@ -9400,9 +8953,7 @@
       <c r="D6" t="n">
         <v>363015</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n">
         <v>-0.0708423747775617</v>
       </c>
@@ -9428,9 +8979,7 @@
       <c r="D7" t="n">
         <v>353264</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n">
         <v>-0.06972197239275799</v>
       </c>
@@ -9456,9 +9005,7 @@
       <c r="D8" t="n">
         <v>352049</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n">
         <v>-0.03435270295230299</v>
       </c>
@@ -9484,9 +9031,7 @@
       <c r="D9" t="n">
         <v>386184</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n">
         <v>-0.06396030832719365</v>
       </c>
@@ -9512,9 +9057,7 @@
       <c r="D10" t="n">
         <v>355165</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n">
         <v>-0.05099077643028005</v>
       </c>
@@ -9540,9 +9083,7 @@
       <c r="D11" t="n">
         <v>363343</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n">
         <v>-0.03079526392958276</v>
       </c>
@@ -9568,9 +9109,7 @@
       <c r="D12" t="n">
         <v>341197</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n">
         <v>-0.02593208237577813</v>
       </c>
@@ -9596,9 +9135,7 @@
       <c r="D13" t="n">
         <v>355306</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n">
         <v>-0.03917727717923605</v>
       </c>
@@ -9624,9 +9161,7 @@
       <c r="D14" t="n">
         <v>331282</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n">
         <v>0.02629945834563453</v>
       </c>
@@ -9652,9 +9187,7 @@
       <c r="D15" t="n">
         <v>320647</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n">
         <v>0.1045935146915895</v>
       </c>
@@ -9680,9 +9213,7 @@
       <c r="D16" t="n">
         <v>189636</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n">
         <v>-0.3819558101472995</v>
       </c>
@@ -9708,9 +9239,7 @@
       <c r="D17" t="n">
         <v>36729</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n">
         <v>-0.8556182953751262</v>
       </c>
@@ -9736,9 +9265,7 @@
       <c r="D18" t="n">
         <v>41426</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n">
         <v>-0.8180307291161608</v>
       </c>
@@ -9764,9 +9291,7 @@
       <c r="D19" t="n">
         <v>53232</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n">
         <v>-0.70536464901219</v>
       </c>
@@ -9792,9 +9317,7 @@
       <c r="D20" t="n">
         <v>60372</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n">
         <v>-0.716813783136627</v>
       </c>
@@ -9820,9 +9343,7 @@
       <c r="D21" t="n">
         <v>62737</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n">
         <v>-0.717155575847506</v>
       </c>
@@ -9848,9 +9369,7 @@
       <c r="D22" t="n">
         <v>67048</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n">
         <v>-0.6701898152479596</v>
       </c>
@@ -9876,9 +9395,7 @@
       <c r="D23" t="n">
         <v>68944</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n">
         <v>-0.6732339332140667</v>
       </c>
@@ -9904,9 +9421,7 @@
       <c r="D24" t="n">
         <v>61408</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n">
         <v>-0.6690317075824471</v>
       </c>
@@ -9932,9 +9447,7 @@
       <c r="D25" t="n">
         <v>60990</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n">
         <v>-0.6819485233602758</v>
       </c>
@@ -9960,9 +9473,7 @@
       <c r="D26" t="n">
         <v>60140</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n">
         <v>-0.6525584426258381</v>
       </c>
@@ -9988,9 +9499,7 @@
       <c r="D27" t="n">
         <v>58779</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n">
         <v>-0.6695877586692145</v>
       </c>
@@ -10016,9 +9525,7 @@
       <c r="D28" t="n">
         <v>74139</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n">
         <v>-0.4055292605441563</v>
       </c>
@@ -10044,9 +9551,7 @@
       <c r="D29" t="n">
         <v>69787</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n">
         <v>1.610084517864003</v>
       </c>
@@ -10072,9 +9577,7 @@
       <c r="D30" t="n">
         <v>70760</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n">
         <v>0.9911775590259788</v>
       </c>
@@ -10100,9 +9603,7 @@
       <c r="D31" t="n">
         <v>77793</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n">
         <v>0.3014712438698172</v>
       </c>
@@ -10128,9 +9629,7 @@
       <c r="D32" t="n">
         <v>77550</v>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n">
         <v>0.2038158136121813</v>
       </c>
@@ -10156,9 +9655,7 @@
       <c r="D33" t="n">
         <v>95360</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n">
         <v>0.373780938929244</v>
       </c>
@@ -10184,9 +9681,7 @@
       <c r="D34" t="n">
         <v>99306</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n">
         <v>0.4234032789620792</v>
       </c>
@@ -10212,9 +9707,7 @@
       <c r="D35" t="n">
         <v>107093</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n">
         <v>0.3046768977844641</v>
       </c>
@@ -10240,9 +9733,7 @@
       <c r="D36" t="n">
         <v>116854</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n">
         <v>0.6063568413038964</v>
       </c>
@@ -10268,9 +9759,7 @@
       <c r="D37" t="n">
         <v>138709</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n">
         <v>0.7871780205013664</v>
       </c>
@@ -10296,9 +9785,7 @@
       <c r="D38" t="n">
         <v>122008</v>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n">
         <v>0.2144721835001901</v>
       </c>
@@ -10324,9 +9811,7 @@
       <c r="D39" t="n">
         <v>254203</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n">
         <v>-0.1968277309040698</v>
       </c>
@@ -10352,9 +9837,7 @@
       <c r="D40" t="n">
         <v>186188</v>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n">
         <v>0.1860518932052877</v>
       </c>
@@ -10380,9 +9863,7 @@
       <c r="D41" t="n">
         <v>231095</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n">
         <v>0.4095421729307261</v>
       </c>
@@ -10408,9 +9889,7 @@
       <c r="D42" t="n">
         <v>251098</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n">
         <v>0.5477868474656913</v>
       </c>
@@ -10436,9 +9915,7 @@
       <c r="D43" t="n">
         <v>253099</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n">
         <v>0.5131542888462592</v>
       </c>
@@ -10464,9 +9941,7 @@
       <c r="D44" t="n">
         <v>258656</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n">
         <v>0.6957759552242941</v>
       </c>
@@ -10492,9 +9967,7 @@
       <c r="D45" t="n">
         <v>271077</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="n">
         <v>0.5820762164709338</v>
       </c>
@@ -10520,9 +9993,7 @@
       <c r="D46" t="n">
         <v>265158</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n">
         <v>0.3614846250337042</v>
       </c>
@@ -10548,9 +10019,7 @@
       <c r="D47" t="n">
         <v>299790</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E47" s="2" t="n"/>
       <c r="F47" s="2" t="n">
         <v>0.5169517718524507</v>
       </c>
@@ -10576,9 +10045,7 @@
       <c r="D48" t="n">
         <v>280295</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n">
         <v>0.3418371193761377</v>
       </c>
@@ -10604,9 +10071,7 @@
       <c r="D49" t="n">
         <v>274780</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n">
         <v>0.2314695333218179</v>
       </c>
@@ -10632,9 +10097,7 @@
       <c r="D50" t="n">
         <v>271687</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E50" s="2" t="n"/>
       <c r="F50" s="2" t="n">
         <v>0.6799257048646619</v>
       </c>
@@ -10660,9 +10123,7 @@
       <c r="D51" t="n">
         <v>260576</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E51" s="2" t="n"/>
       <c r="F51" s="2" t="n">
         <v>1.596548221083537</v>
       </c>
@@ -10688,9 +10149,7 @@
       <c r="D52" t="n">
         <v>297718</v>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n">
         <v>0.6917847474575031</v>
       </c>
@@ -10716,9 +10175,7 @@
       <c r="D53" t="n">
         <v>276772</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n">
         <v>0.4436119667937138</v>
       </c>
@@ -10744,9 +10201,7 @@
       <c r="D54" t="n">
         <v>304408</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n">
         <v>0.482639205759874</v>
       </c>
@@ -10772,9 +10227,7 @@
       <c r="D55" t="n">
         <v>287581</v>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n">
         <v>0.4907860182921308</v>
       </c>
@@ -10800,9 +10253,7 @@
       <c r="D56" t="n">
         <v>328074</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E56" s="2" t="n"/>
       <c r="F56" s="2" t="n">
         <v>0.42248038266567</v>
       </c>
@@ -10828,9 +10279,7 @@
       <c r="D57" t="n">
         <v>354853</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E57" s="2" t="n"/>
       <c r="F57" s="2" t="n">
         <v>0.3558000278512742</v>
       </c>
@@ -10856,9 +10305,7 @@
       <c r="D58" t="n">
         <v>325925</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="n">
         <v>0.3178084314941104</v>
       </c>
@@ -10884,9 +10331,7 @@
       <c r="D59" t="n">
         <v>335998</v>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="n">
         <v>0.2610779146993711</v>
       </c>
@@ -10912,9 +10357,7 @@
       <c r="D60" t="n">
         <v>324531</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="n">
         <v>0.1995946298488892</v>
       </c>
@@ -10940,9 +10383,7 @@
       <c r="D61" t="n">
         <v>312232</v>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="n">
         <v>0.2284488448844884</v>
       </c>
@@ -10968,9 +10409,7 @@
       <c r="D62" t="n">
         <v>291915</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="n">
         <v>0.1295783279708146</v>
       </c>
@@ -10996,9 +10435,7 @@
       <c r="D63" t="n">
         <v>300009</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="n">
         <v>0.1926643765235972</v>
       </c>
@@ -11024,9 +10461,7 @@
       <c r="D64" t="n">
         <v>323430</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="n">
         <v>0.1502344372245228</v>
       </c>
@@ -11052,9 +10487,7 @@
       <c r="D65" t="n">
         <v>292727</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n">
         <v>0.1808206296678059</v>
       </c>
@@ -11080,9 +10513,7 @@
       <c r="D66" t="n">
         <v>315508</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n">
         <v>0.149045625947571</v>
       </c>
@@ -11108,9 +10539,7 @@
       <c r="D67" t="n">
         <v>307762</v>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="n">
         <v>0.02346813260239024</v>
       </c>
@@ -11136,9 +10565,7 @@
       <c r="D68" t="n">
         <v>338006</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="n">
         <v>0.05019584419761311</v>
       </c>
@@ -11164,9 +10591,7 @@
       <c r="D69" t="n">
         <v>353703</v>
       </c>
-      <c r="E69" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E69" s="2" t="n"/>
       <c r="F69" s="2" t="n">
         <v>0.09925077604309322</v>
       </c>
@@ -11192,9 +10617,7 @@
       <c r="D70" t="n">
         <v>330318</v>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n">
         <v>0.08363226502009213</v>
       </c>
@@ -11220,9 +10643,7 @@
       <c r="D71" t="n">
         <v>346933</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E71" s="2" t="n"/>
       <c r="F71" s="2" t="n">
         <v>0.08088961801606979</v>
       </c>
@@ -11248,9 +10669,7 @@
       <c r="D72" t="n">
         <v>317027</v>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="n">
         <v>0.0395168710373555</v>
       </c>
@@ -11276,9 +10695,7 @@
       <c r="D73" t="n">
         <v>318346</v>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E73" s="2" t="n"/>
       <c r="F73" s="2" t="n">
         <v>0.06534777819569072</v>
       </c>
@@ -11304,9 +10721,7 @@
       <c r="D74" t="n">
         <v>304619</v>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E74" s="2" t="n"/>
       <c r="F74" s="2" t="n">
         <v>0.02681618722574354</v>
       </c>
@@ -11332,9 +10747,7 @@
       <c r="D75" t="n">
         <v>273738</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E75" s="2" t="n"/>
       <c r="F75" s="2" t="n">
         <v>-0.1170066653929482</v>
       </c>
@@ -11360,9 +10773,7 @@
       <c r="D76" t="n">
         <v>317779</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E76" s="2" t="n"/>
       <c r="F76" s="2" t="n">
         <v>-0.09354898342205609</v>
       </c>
@@ -11388,9 +10799,7 @@
       <c r="D77" t="n">
         <v>303248</v>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="n">
         <v>-0.1739649791265303</v>
       </c>
@@ -11416,9 +10825,7 @@
       <c r="D78" t="n">
         <v>299344</v>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="n">
         <v>-0.1394195527387141</v>
       </c>
@@ -11444,9 +10851,7 @@
       <c r="D79" t="n">
         <v>304231</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E79" s="2" t="n"/>
       <c r="F79" s="2" t="n">
         <v>-0.09826637624561549</v>
       </c>
@@ -11472,9 +10877,7 @@
       <c r="D80" t="n">
         <v>331296</v>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="n">
         <v>-0.09822102396395017</v>
       </c>
@@ -11500,9 +10903,7 @@
       <c r="D81" t="n">
         <v>340375</v>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="n">
         <v>-0.1049228748737941</v>
       </c>
@@ -11528,9 +10929,7 @@
       <c r="D82" t="n">
         <v>323331</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="n">
         <v>-0.09770296874481819</v>
       </c>
@@ -11556,9 +10955,7 @@
       <c r="D83" t="n">
         <v>341108</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E83" s="2" t="n"/>
       <c r="F83" s="2" t="n">
         <v>-0.08073473611590204</v>
       </c>
@@ -11584,9 +10981,7 @@
       <c r="D84" t="n">
         <v>302866</v>
       </c>
-      <c r="E84" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E84" s="2" t="n"/>
       <c r="F84" s="2" t="n">
         <v>-0.08437829904472539</v>
       </c>
@@ -11612,9 +11007,7 @@
       <c r="D85" t="n">
         <v>300939</v>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E85" s="2" t="n"/>
       <c r="F85" s="2" t="n">
         <v>-0.130133812473403</v>
       </c>
@@ -11640,9 +11033,7 @@
       <c r="D86" t="n">
         <v>289016</v>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E86" s="2" t="n"/>
       <c r="F86" s="2" t="n">
         <v>-0.1254203885782833</v>
       </c>
@@ -11668,9 +11059,7 @@
       <c r="D87" t="n">
         <v>291368</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E87" s="2" t="n"/>
       <c r="F87" s="2" t="n">
         <v>-0.03688991406234052</v>
       </c>
@@ -11696,9 +11085,7 @@
       <c r="D88" t="n">
         <v>329281</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n">
         <v>-0.009799448327353423</v>
       </c>
@@ -11724,9 +11111,7 @@
       <c r="D89" t="n">
         <v>322513</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="n">
         <v>0.0651073628162392</v>
       </c>
@@ -11752,9 +11137,7 @@
       <c r="D90" t="n">
         <v>304982</v>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="n">
         <v>0.1295500932050413</v>
       </c>
@@ -11780,9 +11163,7 @@
       <c r="D91" t="n">
         <v>320046</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E91" s="2" t="n"/>
       <c r="F91" s="2" t="n">
         <v>0.1033507970566167</v>
       </c>
@@ -11819,6 +11200,34 @@
       </c>
       <c r="H92" s="2" t="n">
         <v>-0.01976480247271322</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>195796</v>
+      </c>
+      <c r="C93" t="n">
+        <v>202160</v>
+      </c>
+      <c r="D93" t="n">
+        <v>280955</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>269716</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>-0.4322416762841517</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>0.05400910318507203</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>-0.1745721630554535</v>
       </c>
     </row>
   </sheetData>
@@ -11832,7 +11241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11908,9 +11317,7 @@
       <c r="D2" t="n">
         <v>818</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n">
         <v>-0.03862122992557775</v>
       </c>
@@ -11936,9 +11343,7 @@
       <c r="D3" t="n">
         <v>834</v>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n">
         <v>-0.05785353741137896</v>
       </c>
@@ -11964,9 +11369,7 @@
       <c r="D4" t="n">
         <v>895</v>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n">
         <v>-0.002690899466231417</v>
       </c>
@@ -11992,9 +11395,7 @@
       <c r="D5" t="n">
         <v>980</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n">
         <v>-0.05813555174944948</v>
       </c>
@@ -12020,9 +11421,7 @@
       <c r="D6" t="n">
         <v>1057</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n">
         <v>0.01150242213627623</v>
       </c>
@@ -12048,9 +11447,7 @@
       <c r="D7" t="n">
         <v>969</v>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n">
         <v>-0.007134162382453527</v>
       </c>
@@ -12076,9 +11473,7 @@
       <c r="D8" t="n">
         <v>964</v>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n">
         <v>-0.00480139457084702</v>
       </c>
@@ -12104,9 +11499,7 @@
       <c r="D9" t="n">
         <v>1009</v>
       </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="n">
         <v>-0.02644718088543834</v>
       </c>
@@ -12132,9 +11525,7 @@
       <c r="D10" t="n">
         <v>928</v>
       </c>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n">
         <v>0.01145849535956862</v>
       </c>
@@ -12160,9 +11551,7 @@
       <c r="D11" t="n">
         <v>1019</v>
       </c>
-      <c r="E11" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n">
         <v>-0.02762300871066468</v>
       </c>
@@ -12188,9 +11577,7 @@
       <c r="D12" t="n">
         <v>916</v>
       </c>
-      <c r="E12" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n">
         <v>-0.01189702249382395</v>
       </c>
@@ -12216,9 +11603,7 @@
       <c r="D13" t="n">
         <v>757</v>
       </c>
-      <c r="E13" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n">
         <v>0.02478664969781113</v>
       </c>
@@ -12244,9 +11629,7 @@
       <c r="D14" t="n">
         <v>833</v>
       </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="n">
         <v>-0.02470473195797224</v>
       </c>
@@ -12272,9 +11655,7 @@
       <c r="D15" t="n">
         <v>806</v>
       </c>
-      <c r="E15" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="n">
         <v>0.04977511396939108</v>
       </c>
@@ -12300,9 +11681,7 @@
       <c r="D16" t="n">
         <v>823</v>
       </c>
-      <c r="E16" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" s="2" t="n"/>
       <c r="F16" s="2" t="n">
         <v>-0.1462314225053079</v>
       </c>
@@ -12328,9 +11707,7 @@
       <c r="D17" t="n">
         <v>441</v>
       </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E17" s="2" t="n"/>
       <c r="F17" s="2" t="n">
         <v>-0.5111209775313272</v>
       </c>
@@ -12356,9 +11733,7 @@
       <c r="D18" t="n">
         <v>510</v>
       </c>
-      <c r="E18" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n">
         <v>-0.4635724477435652</v>
       </c>
@@ -12384,9 +11759,7 @@
       <c r="D19" t="n">
         <v>573</v>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="n">
         <v>-0.09294795507313415</v>
       </c>
@@ -12412,9 +11785,7 @@
       <c r="D20" t="n">
         <v>684</v>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n">
         <v>0.01895904946565349</v>
       </c>
@@ -12440,9 +11811,7 @@
       <c r="D21" t="n">
         <v>894</v>
       </c>
-      <c r="E21" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n">
         <v>-0.03881389607496352</v>
       </c>
@@ -12468,9 +11837,7 @@
       <c r="D22" t="n">
         <v>1854</v>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="n">
         <v>-0.0143530859134714</v>
       </c>
@@ -12496,9 +11863,7 @@
       <c r="D23" t="n">
         <v>1595</v>
       </c>
-      <c r="E23" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="n">
         <v>-0.0454227530734673</v>
       </c>
@@ -12524,9 +11889,7 @@
       <c r="D24" t="n">
         <v>1513</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="n">
         <v>-0.06352391604710836</v>
       </c>
@@ -12552,9 +11915,7 @@
       <c r="D25" t="n">
         <v>1738</v>
       </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="n">
         <v>-0.004419164767106791</v>
       </c>
@@ -12580,9 +11941,7 @@
       <c r="D26" t="n">
         <v>2185</v>
       </c>
-      <c r="E26" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="n">
         <v>-0.05832800904310217</v>
       </c>
@@ -12608,9 +11967,7 @@
       <c r="D27" t="n">
         <v>1525</v>
       </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="n">
         <v>-0.1279716178687229</v>
       </c>
@@ -12636,9 +11993,7 @@
       <c r="D28" t="n">
         <v>2265</v>
       </c>
-      <c r="E28" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="n">
         <v>0.1294995337270749</v>
       </c>
@@ -12664,9 +12019,7 @@
       <c r="D29" t="n">
         <v>1256</v>
       </c>
-      <c r="E29" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n">
         <v>0.7789843870768279</v>
       </c>
@@ -12692,9 +12045,7 @@
       <c r="D30" t="n">
         <v>1184</v>
       </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n">
         <v>0.4651762682717111</v>
       </c>
@@ -12720,9 +12071,7 @@
       <c r="D31" t="n">
         <v>1400</v>
       </c>
-      <c r="E31" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="n">
         <v>-0.0234978413276825</v>
       </c>
@@ -12748,9 +12097,7 @@
       <c r="D32" t="n">
         <v>1503</v>
       </c>
-      <c r="E32" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="n">
         <v>-0.0805212742701564</v>
       </c>
@@ -12776,9 +12123,7 @@
       <c r="D33" t="n">
         <v>1670</v>
       </c>
-      <c r="E33" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="n">
         <v>-0.0722529681661227</v>
       </c>
@@ -12804,9 +12149,7 @@
       <c r="D34" t="n">
         <v>1396</v>
       </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n">
         <v>-0.1190876940824933</v>
       </c>
@@ -12832,9 +12175,7 @@
       <c r="D35" t="n">
         <v>2249</v>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E35" s="2" t="n"/>
       <c r="F35" s="2" t="n">
         <v>-0.07819376535294753</v>
       </c>
@@ -12860,9 +12201,7 @@
       <c r="D36" t="n">
         <v>2152</v>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n">
         <v>0.01277168049219899</v>
       </c>
@@ -12888,9 +12227,7 @@
       <c r="D37" t="n">
         <v>2117</v>
       </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="n">
         <v>-0.001587593014590736</v>
       </c>
@@ -12916,9 +12253,7 @@
       <c r="D38" t="n">
         <v>1635</v>
       </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="n">
         <v>-0.07135102973872924</v>
       </c>
@@ -12944,9 +12279,7 @@
       <c r="D39" t="n">
         <v>2073</v>
       </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n">
         <v>-0.2392134413054473</v>
       </c>
@@ -12972,9 +12305,7 @@
       <c r="D40" t="n">
         <v>2119</v>
       </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E40" s="2" t="n"/>
       <c r="F40" s="2" t="n">
         <v>-0.01415033758990166</v>
       </c>
@@ -13000,9 +12331,7 @@
       <c r="D41" t="n">
         <v>2157</v>
       </c>
-      <c r="E41" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="n">
         <v>0.05725783676927421</v>
       </c>
@@ -13028,9 +12357,7 @@
       <c r="D42" t="n">
         <v>1981</v>
       </c>
-      <c r="E42" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E42" s="2" t="n"/>
       <c r="F42" s="2" t="n">
         <v>0.08446864990566452</v>
       </c>
@@ -13056,9 +12383,7 @@
       <c r="D43" t="n">
         <v>1716</v>
       </c>
-      <c r="E43" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E43" s="2" t="n"/>
       <c r="F43" s="2" t="n">
         <v>0.01022663894944988</v>
       </c>
@@ -13084,9 +12409,7 @@
       <c r="D44" t="n">
         <v>1453</v>
       </c>
-      <c r="E44" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n">
         <v>-0.0144054379717835</v>
       </c>
@@ -13112,9 +12435,7 @@
       <c r="D45" t="n">
         <v>1662</v>
       </c>
-      <c r="E45" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="n">
         <v>0.07013026741784995</v>
       </c>
@@ -13140,9 +12461,7 @@
       <c r="D46" t="n">
         <v>1540</v>
       </c>
-      <c r="E46" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="n">
         <v>0.06887612709317303</v>
       </c>
@@ -13168,9 +12487,7 @@
       <c r="D47" t="n">
         <v>1667</v>
       </c>
-      <c r="E47" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E47" s="2" t="n"/>
       <c r="F47" s="2" t="n">
         <v>0.02042708869402168</v>
       </c>
@@ -13196,9 +12513,7 @@
       <c r="D48" t="n">
         <v>1628</v>
       </c>
-      <c r="E48" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E48" s="2" t="n"/>
       <c r="F48" s="2" t="n">
         <v>0.02652937853667238</v>
       </c>
@@ -13224,9 +12539,7 @@
       <c r="D49" t="n">
         <v>1626</v>
       </c>
-      <c r="E49" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="n">
         <v>-0.01177984985829565</v>
       </c>
@@ -13252,9 +12565,7 @@
       <c r="D50" t="n">
         <v>1597</v>
       </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E50" s="2" t="n"/>
       <c r="F50" s="2" t="n">
         <v>0.1440446015590313</v>
       </c>
@@ -13280,9 +12591,7 @@
       <c r="D51" t="n">
         <v>1579</v>
       </c>
-      <c r="E51" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E51" s="2" t="n"/>
       <c r="F51" s="2" t="n">
         <v>0.3940591600125655</v>
       </c>
@@ -13308,9 +12617,7 @@
       <c r="D52" t="n">
         <v>1817</v>
       </c>
-      <c r="E52" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="n">
         <v>0.05007653619068445</v>
       </c>
@@ -13336,9 +12643,7 @@
       <c r="D53" t="n">
         <v>1543</v>
       </c>
-      <c r="E53" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="n">
         <v>0.04655451393347888</v>
       </c>
@@ -13364,9 +12669,7 @@
       <c r="D54" t="n">
         <v>1753</v>
       </c>
-      <c r="E54" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E54" s="2" t="n"/>
       <c r="F54" s="2" t="n">
         <v>0.1518644204947175</v>
       </c>
@@ -13392,9 +12695,7 @@
       <c r="D55" t="n">
         <v>1841</v>
       </c>
-      <c r="E55" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="n">
         <v>0.1430887290649294</v>
       </c>
@@ -13420,9 +12721,7 @@
       <c r="D56" t="n">
         <v>1663</v>
       </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E56" s="2" t="n"/>
       <c r="F56" s="2" t="n">
         <v>0.1820364796631634</v>
       </c>
@@ -13448,9 +12747,7 @@
       <c r="D57" t="n">
         <v>1585</v>
       </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E57" s="2" t="n"/>
       <c r="F57" s="2" t="n">
         <v>0.169817523464672</v>
       </c>
@@ -13476,9 +12773,7 @@
       <c r="D58" t="n">
         <v>1507</v>
       </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="n">
         <v>0.1073847745200926</v>
       </c>
@@ -13504,9 +12799,7 @@
       <c r="D59" t="n">
         <v>1322</v>
       </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="n">
         <v>0.07119959254598837</v>
       </c>
@@ -13532,9 +12825,7 @@
       <c r="D60" t="n">
         <v>1177</v>
       </c>
-      <c r="E60" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E60" s="2" t="n"/>
       <c r="F60" s="2" t="n">
         <v>0.03174235403151066</v>
       </c>
@@ -13560,9 +12851,7 @@
       <c r="D61" t="n">
         <v>1089</v>
       </c>
-      <c r="E61" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="n">
         <v>-0.03020020359687818</v>
       </c>
@@ -13588,9 +12877,7 @@
       <c r="D62" t="n">
         <v>1459</v>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="n">
         <v>0.01782266740682154</v>
       </c>
@@ -13616,9 +12903,7 @@
       <c r="D63" t="n">
         <v>1510</v>
       </c>
-      <c r="E63" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="n">
         <v>0.07096104767245039</v>
       </c>
@@ -13644,9 +12929,7 @@
       <c r="D64" t="n">
         <v>1578</v>
       </c>
-      <c r="E64" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E64" s="2" t="n"/>
       <c r="F64" s="2" t="n">
         <v>-0.08815918899040294</v>
       </c>
@@ -13672,9 +12955,7 @@
       <c r="D65" t="n">
         <v>1640</v>
       </c>
-      <c r="E65" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="n">
         <v>0.01814585398894659</v>
       </c>
@@ -13700,9 +12981,7 @@
       <c r="D66" t="n">
         <v>1538</v>
       </c>
-      <c r="E66" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="n">
         <v>-0.09266015973164381</v>
       </c>
@@ -13728,9 +13007,7 @@
       <c r="D67" t="n">
         <v>1319</v>
       </c>
-      <c r="E67" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="n">
         <v>-0.1376379211176824</v>
       </c>
@@ -13756,9 +13033,7 @@
       <c r="D68" t="n">
         <v>1405</v>
       </c>
-      <c r="E68" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="n">
         <v>-0.1769886877513253</v>
       </c>
@@ -13784,9 +13059,7 @@
       <c r="D69" t="n">
         <v>1387</v>
       </c>
-      <c r="E69" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E69" s="2" t="n"/>
       <c r="F69" s="2" t="n">
         <v>-0.2374385520479936</v>
       </c>
@@ -13812,9 +13085,7 @@
       <c r="D70" t="n">
         <v>1416</v>
       </c>
-      <c r="E70" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n">
         <v>-0.1737833217707526</v>
       </c>
@@ -13840,9 +13111,7 @@
       <c r="D71" t="n">
         <v>1490</v>
       </c>
-      <c r="E71" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E71" s="2" t="n"/>
       <c r="F71" s="2" t="n">
         <v>-0.1308226936469535</v>
       </c>
@@ -13868,9 +13137,7 @@
       <c r="D72" t="n">
         <v>1327</v>
       </c>
-      <c r="E72" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="n">
         <v>-0.219201474661277</v>
       </c>
@@ -13896,9 +13163,7 @@
       <c r="D73" t="n">
         <v>1303</v>
       </c>
-      <c r="E73" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E73" s="2" t="n"/>
       <c r="F73" s="2" t="n">
         <v>-0.1395121786044832</v>
       </c>
@@ -13924,9 +13189,7 @@
       <c r="D74" t="n">
         <v>1440</v>
       </c>
-      <c r="E74" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E74" s="2" t="n"/>
       <c r="F74" s="2" t="n">
         <v>-0.1879009020749171</v>
       </c>
@@ -13952,9 +13215,7 @@
       <c r="D75" t="n">
         <v>1491</v>
       </c>
-      <c r="E75" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E75" s="2" t="n"/>
       <c r="F75" s="2" t="n">
         <v>-0.2473282965688673</v>
       </c>
@@ -13980,9 +13241,7 @@
       <c r="D76" t="n">
         <v>1610</v>
       </c>
-      <c r="E76" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E76" s="2" t="n"/>
       <c r="F76" s="2" t="n">
         <v>-0.1512558492106299</v>
       </c>
@@ -14008,9 +13267,7 @@
       <c r="D77" t="n">
         <v>1466</v>
       </c>
-      <c r="E77" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="n">
         <v>-0.2712705184756671</v>
       </c>
@@ -14036,9 +13293,7 @@
       <c r="D78" t="n">
         <v>1273</v>
       </c>
-      <c r="E78" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="n">
         <v>-0.2647142794926761</v>
       </c>
@@ -14064,9 +13319,7 @@
       <c r="D79" t="n">
         <v>1309</v>
       </c>
-      <c r="E79" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E79" s="2" t="n"/>
       <c r="F79" s="2" t="n">
         <v>-0.247488658870011</v>
       </c>
@@ -14092,9 +13345,7 @@
       <c r="D80" t="n">
         <v>1419</v>
       </c>
-      <c r="E80" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="n">
         <v>-0.1407687929353554</v>
       </c>
@@ -14120,9 +13371,7 @@
       <c r="D81" t="n">
         <v>1310</v>
       </c>
-      <c r="E81" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="n">
         <v>-0.2090859566104447</v>
       </c>
@@ -14148,9 +13397,7 @@
       <c r="D82" t="n">
         <v>1512</v>
       </c>
-      <c r="E82" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="n">
         <v>-0.1277845159236717</v>
       </c>
@@ -14176,9 +13423,7 @@
       <c r="D83" t="n">
         <v>1676</v>
       </c>
-      <c r="E83" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E83" s="2" t="n"/>
       <c r="F83" s="2" t="n">
         <v>-0.1038334888610012</v>
       </c>
@@ -14204,9 +13449,7 @@
       <c r="D84" t="n">
         <v>1305</v>
       </c>
-      <c r="E84" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E84" s="2" t="n"/>
       <c r="F84" s="2" t="n">
         <v>-0.1364962760124872</v>
       </c>
@@ -14232,9 +13475,7 @@
       <c r="D85" t="n">
         <v>1189</v>
       </c>
-      <c r="E85" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E85" s="2" t="n"/>
       <c r="F85" s="2" t="n">
         <v>-0.07873421872438105</v>
       </c>
@@ -14260,9 +13501,7 @@
       <c r="D86" t="n">
         <v>1126</v>
       </c>
-      <c r="E86" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E86" s="2" t="n"/>
       <c r="F86" s="2" t="n">
         <v>-0.1801162500445744</v>
       </c>
@@ -14288,9 +13527,7 @@
       <c r="D87" t="n">
         <v>1299</v>
       </c>
-      <c r="E87" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E87" s="2" t="n"/>
       <c r="F87" s="2" t="n">
         <v>-0.03106898367561875</v>
       </c>
@@ -14316,9 +13553,7 @@
       <c r="D88" t="n">
         <v>1583</v>
       </c>
-      <c r="E88" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="n">
         <v>-0.01212006709834029</v>
       </c>
@@ -14344,9 +13579,7 @@
       <c r="D89" t="n">
         <v>1190</v>
       </c>
-      <c r="E89" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="n">
         <v>0.1294488105633617</v>
       </c>
@@ -14372,9 +13605,7 @@
       <c r="D90" t="n">
         <v>1189</v>
       </c>
-      <c r="E90" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="n">
         <v>0.2368492059835866</v>
       </c>
@@ -14400,9 +13631,7 @@
       <c r="D91" t="n">
         <v>1402</v>
       </c>
-      <c r="E91" s="2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E91" s="2" t="n"/>
       <c r="F91" s="2" t="n">
         <v>0.3565629228687415</v>
       </c>
@@ -14439,6 +13668,34 @@
       </c>
       <c r="H92" s="2" t="n">
         <v>-0.200845665961945</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>August 2026</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>149649</v>
+      </c>
+      <c r="C93" t="n">
+        <v>131581</v>
+      </c>
+      <c r="D93" t="n">
+        <v>952</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>73791</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0.01055467768728982</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>-0.2718181717561899</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>-0.2732824427480916</v>
       </c>
     </row>
   </sheetData>
@@ -14447,6 +13704,291 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>month_2025</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>month_2026</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ambassador Bridge (Detroit)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>492944</v>
+      </c>
+      <c r="C2" t="n">
+        <v>345445</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-0.2992206011230484</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Blue Water Bridge (Port Huron)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>372862</v>
+      </c>
+      <c r="C3" t="n">
+        <v>333986</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.104263775874184</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Detroit-Windsor Tunnel</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>343114</v>
+      </c>
+      <c r="C4" t="n">
+        <v>282880</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.1755509830551945</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>343507</v>
+      </c>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ambassador Bridge (Detroit)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>344858</v>
+      </c>
+      <c r="C6" t="n">
+        <v>195796</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.4322416762841517</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Blue Water Bridge (Port Huron)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>191801</v>
+      </c>
+      <c r="C7" t="n">
+        <v>202160</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.05400910318507203</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Detroit-Windsor Tunnel</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>340375</v>
+      </c>
+      <c r="C8" t="n">
+        <v>280955</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.1745721630554535</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>269716</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ambassador Bridge (Detroit)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>148086</v>
+      </c>
+      <c r="C10" t="n">
+        <v>149649</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.01055467768728982</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Blue Water Bridge (Port Huron)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>180698</v>
+      </c>
+      <c r="C11" t="n">
+        <v>131581</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>-0.2718181717561899</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Detroit-Windsor Tunnel</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1310</v>
+      </c>
+      <c r="C12" t="n">
+        <v>952</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-0.2732824427480916</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>73791</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14524,7 +14066,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-11 20:09 UTC</t>
+          <t>Rebuilt: 2026-09-14 15:32 UTC</t>
         </is>
       </c>
     </row>

--- a/data/btoa_traffic_analysis.xlsx
+++ b/data/btoa_traffic_analysis.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Car traffic" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Truck traffic" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall traffic" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="August 2026" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Chart Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Car traffic" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Truck traffic" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Overall traffic" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="August 2026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14066,7 +14066,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-14 15:40 UTC</t>
+          <t>Rebuilt: 2026-09-14 16:31 UTC</t>
         </is>
       </c>
     </row>

--- a/data/btoa_traffic_analysis.xlsx
+++ b/data/btoa_traffic_analysis.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Truck traffic" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Overall traffic" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="August 2026" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Methodology" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="September 2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F277"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6294,6 +6295,78 @@
         </is>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>174577</v>
+      </c>
+      <c r="C278" t="n">
+        <v>161881</v>
+      </c>
+      <c r="D278" t="n">
+        <v>259965</v>
+      </c>
+      <c r="E278" t="n">
+        <v>230283</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Passenger cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>143102</v>
+      </c>
+      <c r="C279" t="n">
+        <v>125623</v>
+      </c>
+      <c r="D279" t="n">
+        <v>986</v>
+      </c>
+      <c r="E279" t="n">
+        <v>85624</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>317679</v>
+      </c>
+      <c r="C280" t="n">
+        <v>287753</v>
+      </c>
+      <c r="D280" t="n">
+        <v>261902</v>
+      </c>
+      <c r="E280" t="n">
+        <v>315907</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Total vehicles</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6305,7 +6378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8762,6 +8835,34 @@
         <v>-0.1745721630554535</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>174577</v>
+      </c>
+      <c r="C94" t="n">
+        <v>161881</v>
+      </c>
+      <c r="D94" t="n">
+        <v>259965</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>230283</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-0.4166805888760433</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>0.1212614459667253</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>-0.1959787338671516</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8773,7 +8874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11230,6 +11331,34 @@
         <v>-0.2732824427480916</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>143102</v>
+      </c>
+      <c r="C94" t="n">
+        <v>125623</v>
+      </c>
+      <c r="D94" t="n">
+        <v>986</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>85624</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-0.09958534943276558</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>-0.3234362713945648</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>-0.3478835978835979</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11241,7 +11370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -13696,6 +13825,34 @@
       </c>
       <c r="H93" s="2" t="n">
         <v>-0.1755509830551945</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>September 2026</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>317679</v>
+      </c>
+      <c r="C94" t="n">
+        <v>287753</v>
+      </c>
+      <c r="D94" t="n">
+        <v>261902</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>315907</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>-0.3066971329802209</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>-0.1286575561483886</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>-0.1949007697415341</v>
       </c>
     </row>
   </sheetData>
@@ -13994,6 +14151,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>crossing</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>month_2025</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>month_2026</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>pct_change</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ambassador Bridge (Detroit)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>299282</v>
+      </c>
+      <c r="C2" t="n">
+        <v>174577</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>-0.4166805888760433</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Blue Water Bridge (Port Huron)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>144374</v>
+      </c>
+      <c r="C3" t="n">
+        <v>161881</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.1212614459667253</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Detroit-Windsor Tunnel</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>323331</v>
+      </c>
+      <c r="C4" t="n">
+        <v>259965</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.1959787338671516</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>230283</v>
+      </c>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Cars</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ambassador Bridge (Detroit)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>158929</v>
+      </c>
+      <c r="C6" t="n">
+        <v>143102</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.09958534943276558</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Blue Water Bridge (Port Huron)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>185678</v>
+      </c>
+      <c r="C7" t="n">
+        <v>125623</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.3234362713945648</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Detroit-Windsor Tunnel</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C8" t="n">
+        <v>986</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.3478835978835979</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>85624</v>
+      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Trucks</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ambassador Bridge (Detroit)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>458211</v>
+      </c>
+      <c r="C10" t="n">
+        <v>317679</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>-0.3066971329802209</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Blue Water Bridge (Port Huron)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>330241</v>
+      </c>
+      <c r="C11" t="n">
+        <v>287753</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>-0.1286575561483886</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Detroit-Windsor Tunnel</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>325304</v>
+      </c>
+      <c r="C12" t="n">
+        <v>261902</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-0.1949007697415341</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gordie Howe International Bridge</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>315907</v>
+      </c>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14066,7 +14508,7 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Rebuilt: 2026-09-14 16:31 UTC</t>
+          <t>Rebuilt: 2026-10-19 19:44 UTC</t>
         </is>
       </c>
     </row>
